--- a/output/df_padres_final.xlsx
+++ b/output/df_padres_final.xlsx
@@ -474,12 +474,12 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Indice_Conocimiento</t>
+          <t>Indice_Conocimiento_Norm</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Indice_Acompanamiento</t>
+          <t>Indice_Acompanamiento_Norm</t>
         </is>
       </c>
     </row>
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M2" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="3">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M3" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="4">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>65</v>
+        <v>87.83783783783784</v>
       </c>
     </row>
     <row r="5">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="6">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M6" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="7">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>56.75675675675676</v>
       </c>
     </row>
     <row r="8">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>36.48648648648648</v>
       </c>
     </row>
     <row r="9">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>18</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="M9" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="10">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M10" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="11">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M11" t="n">
-        <v>47</v>
+        <v>63.51351351351351</v>
       </c>
     </row>
     <row r="12">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M12" t="n">
-        <v>47</v>
+        <v>63.51351351351351</v>
       </c>
     </row>
     <row r="13">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M13" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="14">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M14" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="15">
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M15" t="n">
-        <v>46</v>
+        <v>62.16216216216216</v>
       </c>
     </row>
     <row r="16">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M16" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="17">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>37.83783783783784</v>
       </c>
     </row>
     <row r="18">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M18" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="19">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M19" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="20">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M20" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="21">
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M21" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="22">
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="23">
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M23" t="n">
-        <v>68</v>
+        <v>91.8918918918919</v>
       </c>
     </row>
     <row r="24">
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="25">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M25" t="n">
-        <v>46</v>
+        <v>62.16216216216216</v>
       </c>
     </row>
     <row r="26">
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M26" t="n">
-        <v>47</v>
+        <v>63.51351351351351</v>
       </c>
     </row>
     <row r="27">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M27" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="28">
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M28" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="29">
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M29" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="30">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M30" t="n">
-        <v>48</v>
+        <v>64.86486486486487</v>
       </c>
     </row>
     <row r="31">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M31" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="32">
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M32" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="33">
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M33" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="34">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M34" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="35">
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>16</v>
+        <v>84.21052631578947</v>
       </c>
       <c r="M35" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="36">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M36" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="37">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M37" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="38">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>16</v>
+        <v>84.21052631578947</v>
       </c>
       <c r="M38" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="39">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M39" t="n">
-        <v>48</v>
+        <v>64.86486486486487</v>
       </c>
     </row>
     <row r="40">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M40" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="41">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M41" t="n">
-        <v>33</v>
+        <v>44.5945945945946</v>
       </c>
     </row>
     <row r="42">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M42" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="43">
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M43" t="n">
-        <v>35</v>
+        <v>47.2972972972973</v>
       </c>
     </row>
     <row r="44">
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M44" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="45">
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M45" t="n">
-        <v>65</v>
+        <v>87.83783783783784</v>
       </c>
     </row>
     <row r="46">
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M46" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="47">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M47" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="48">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M48" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="49">
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M49" t="n">
-        <v>73</v>
+        <v>98.64864864864865</v>
       </c>
     </row>
     <row r="50">
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M50" t="n">
-        <v>73</v>
+        <v>98.64864864864865</v>
       </c>
     </row>
     <row r="51">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M51" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="52">
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M52" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="53">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M53" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="54">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M54" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M55" t="n">
-        <v>48</v>
+        <v>64.86486486486487</v>
       </c>
     </row>
     <row r="56">
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M56" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="57">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M57" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="58">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M58" t="n">
-        <v>44</v>
+        <v>59.45945945945946</v>
       </c>
     </row>
     <row r="59">
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M59" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="60">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M60" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="61">
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M61" t="n">
-        <v>33</v>
+        <v>44.5945945945946</v>
       </c>
     </row>
     <row r="62">
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M62" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="63">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M63" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="64">
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M64" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="65">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M65" t="n">
-        <v>31</v>
+        <v>41.89189189189189</v>
       </c>
     </row>
     <row r="66">
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M66" t="n">
-        <v>32</v>
+        <v>43.24324324324324</v>
       </c>
     </row>
     <row r="67">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M67" t="n">
-        <v>42</v>
+        <v>56.75675675675676</v>
       </c>
     </row>
     <row r="68">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M68" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="69">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M69" t="n">
-        <v>43</v>
+        <v>58.10810810810811</v>
       </c>
     </row>
     <row r="70">
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M70" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="71">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M71" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="72">
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M72" t="n">
-        <v>31</v>
+        <v>41.89189189189189</v>
       </c>
     </row>
     <row r="73">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M73" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="74">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M74" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75">
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M75" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="76">
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M76" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="77">
@@ -5265,10 +5265,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M77" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="78">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M78" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="79">
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M79" t="n">
-        <v>31</v>
+        <v>41.89189189189189</v>
       </c>
     </row>
     <row r="80">
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>1.351351351351351</v>
       </c>
     </row>
     <row r="81">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M81" t="n">
-        <v>68</v>
+        <v>91.8918918918919</v>
       </c>
     </row>
     <row r="82">
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M82" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="83">
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M83" t="n">
-        <v>29</v>
+        <v>39.18918918918919</v>
       </c>
     </row>
     <row r="84">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M84" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="85">
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M85" t="n">
-        <v>32</v>
+        <v>43.24324324324324</v>
       </c>
     </row>
     <row r="86">
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M86" t="n">
-        <v>23</v>
+        <v>31.08108108108108</v>
       </c>
     </row>
     <row r="87">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M87" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="88">
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M88" t="n">
-        <v>17</v>
+        <v>22.97297297297298</v>
       </c>
     </row>
     <row r="89">
@@ -6021,10 +6021,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M89" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="90">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M90" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="91">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M91" t="n">
-        <v>28</v>
+        <v>37.83783783783784</v>
       </c>
     </row>
     <row r="92">
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M92" t="n">
-        <v>40</v>
+        <v>54.05405405405406</v>
       </c>
     </row>
     <row r="93">
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M93" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="94">
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M94" t="n">
-        <v>43</v>
+        <v>58.10810810810811</v>
       </c>
     </row>
     <row r="95">
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M95" t="n">
-        <v>33</v>
+        <v>44.5945945945946</v>
       </c>
     </row>
     <row r="96">
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M96" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="97">
@@ -6525,10 +6525,10 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M97" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="98">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M98" t="n">
-        <v>65</v>
+        <v>87.83783783783784</v>
       </c>
     </row>
     <row r="99">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M99" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="100">
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M100" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="101">
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M101" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="102">
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M102" t="n">
-        <v>38</v>
+        <v>51.35135135135135</v>
       </c>
     </row>
     <row r="103">
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M103" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="104">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M104" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="105">
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M105" t="n">
-        <v>65</v>
+        <v>87.83783783783784</v>
       </c>
     </row>
     <row r="106">
@@ -7092,10 +7092,10 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M106" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="107">
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M107" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="108">
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M108" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="109">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M109" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="110">
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M110" t="n">
-        <v>38</v>
+        <v>51.35135135135135</v>
       </c>
     </row>
     <row r="111">
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M111" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="112">
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M112" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="113">
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M113" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="114">
@@ -7596,10 +7596,10 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M114" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="115">
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M115" t="n">
-        <v>19</v>
+        <v>25.67567567567567</v>
       </c>
     </row>
     <row r="116">
@@ -7722,10 +7722,10 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M116" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="117">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M117" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="118">
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M118" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119">
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M119" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="120">
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M120" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="121">
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M121" t="n">
-        <v>45</v>
+        <v>60.81081081081081</v>
       </c>
     </row>
     <row r="122">
@@ -8100,10 +8100,10 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M122" t="n">
-        <v>29</v>
+        <v>39.18918918918919</v>
       </c>
     </row>
     <row r="123">
@@ -8163,10 +8163,10 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M123" t="n">
-        <v>32</v>
+        <v>43.24324324324324</v>
       </c>
     </row>
     <row r="124">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>16</v>
+        <v>84.21052631578947</v>
       </c>
       <c r="M124" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="125">
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M125" t="n">
-        <v>43</v>
+        <v>58.10810810810811</v>
       </c>
     </row>
     <row r="126">
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M126" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="127">
@@ -8415,10 +8415,10 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M127" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="128">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M128" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="129">
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M129" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="130">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M130" t="n">
-        <v>35</v>
+        <v>47.2972972972973</v>
       </c>
     </row>
     <row r="131">
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M131" t="n">
-        <v>45</v>
+        <v>60.81081081081081</v>
       </c>
     </row>
     <row r="132">
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M132" t="n">
-        <v>12</v>
+        <v>16.21621621621622</v>
       </c>
     </row>
     <row r="133">
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M133" t="n">
-        <v>25</v>
+        <v>33.78378378378378</v>
       </c>
     </row>
     <row r="134">
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M134" t="n">
-        <v>26</v>
+        <v>35.13513513513514</v>
       </c>
     </row>
     <row r="135">
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M135" t="n">
-        <v>40</v>
+        <v>54.05405405405406</v>
       </c>
     </row>
     <row r="136">
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M136" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="137">
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="M137" t="n">
-        <v>20</v>
+        <v>27.02702702702703</v>
       </c>
     </row>
     <row r="138">
@@ -9108,10 +9108,10 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M138" t="n">
-        <v>27</v>
+        <v>36.48648648648648</v>
       </c>
     </row>
     <row r="139">
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M139" t="n">
-        <v>36</v>
+        <v>48.64864864864865</v>
       </c>
     </row>
     <row r="140">
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="M140" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141">
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M141" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="142">
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M142" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="143">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M143" t="n">
-        <v>45</v>
+        <v>60.81081081081081</v>
       </c>
     </row>
     <row r="144">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M144" t="n">
-        <v>48</v>
+        <v>64.86486486486487</v>
       </c>
     </row>
     <row r="145">
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>18</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="M145" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="146">
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M146" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="147">
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M147" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="148">
@@ -9738,10 +9738,10 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>18</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="M148" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="149">
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M149" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="150">
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M150" t="n">
-        <v>39</v>
+        <v>52.70270270270269</v>
       </c>
     </row>
     <row r="151">
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M151" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M152" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="153">
@@ -10053,10 +10053,10 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M153" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="154">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M154" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="155">
@@ -10179,10 +10179,10 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M155" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="156">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M156" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="157">
@@ -10305,10 +10305,10 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M157" t="n">
-        <v>32</v>
+        <v>43.24324324324324</v>
       </c>
     </row>
     <row r="158">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M158" t="n">
-        <v>34</v>
+        <v>45.94594594594595</v>
       </c>
     </row>
     <row r="159">
@@ -10431,10 +10431,10 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M159" t="n">
-        <v>48</v>
+        <v>64.86486486486487</v>
       </c>
     </row>
     <row r="160">
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M160" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="161">
@@ -10557,10 +10557,10 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M161" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="162">
@@ -10620,10 +10620,10 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M162" t="n">
-        <v>68</v>
+        <v>91.8918918918919</v>
       </c>
     </row>
     <row r="163">
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M163" t="n">
-        <v>40</v>
+        <v>54.05405405405406</v>
       </c>
     </row>
     <row r="164">
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M164" t="n">
-        <v>7</v>
+        <v>9.45945945945946</v>
       </c>
     </row>
     <row r="165">
@@ -10809,10 +10809,10 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M165" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="166">
@@ -10872,10 +10872,10 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M166" t="n">
-        <v>48</v>
+        <v>64.86486486486487</v>
       </c>
     </row>
     <row r="167">
@@ -10935,10 +10935,10 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M167" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="168">
@@ -10998,10 +10998,10 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M168" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="169">
@@ -11061,10 +11061,10 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M169" t="n">
-        <v>39</v>
+        <v>52.70270270270269</v>
       </c>
     </row>
     <row r="170">
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M170" t="n">
-        <v>15</v>
+        <v>20.27027027027027</v>
       </c>
     </row>
     <row r="171">
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M171" t="n">
-        <v>46</v>
+        <v>62.16216216216216</v>
       </c>
     </row>
     <row r="172">
@@ -11250,10 +11250,10 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="M172" t="n">
-        <v>34</v>
+        <v>45.94594594594595</v>
       </c>
     </row>
     <row r="173">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M173" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="174">
@@ -11376,10 +11376,10 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M174" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="175">
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M175" t="n">
-        <v>18</v>
+        <v>24.32432432432433</v>
       </c>
     </row>
     <row r="176">
@@ -11502,10 +11502,10 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M176" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="177">
@@ -11565,10 +11565,10 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="M177" t="n">
-        <v>6</v>
+        <v>8.108108108108109</v>
       </c>
     </row>
     <row r="178">
@@ -11628,10 +11628,10 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M178" t="n">
-        <v>28</v>
+        <v>37.83783783783784</v>
       </c>
     </row>
     <row r="179">
@@ -11691,10 +11691,10 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M179" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="180">
@@ -11754,10 +11754,10 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M180" t="n">
-        <v>27</v>
+        <v>36.48648648648648</v>
       </c>
     </row>
     <row r="181">
@@ -11817,10 +11817,10 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M181" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="182">
@@ -11880,10 +11880,10 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M182" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="183">
@@ -11943,10 +11943,10 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M183" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="184">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M184" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="185">
@@ -12069,10 +12069,10 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M185" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186">
@@ -12132,10 +12132,10 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M186" t="n">
-        <v>29</v>
+        <v>39.18918918918919</v>
       </c>
     </row>
     <row r="187">
@@ -12195,10 +12195,10 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M187" t="n">
-        <v>46</v>
+        <v>62.16216216216216</v>
       </c>
     </row>
     <row r="188">
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M188" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="189">
@@ -12321,10 +12321,10 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M189" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="190">
@@ -12384,10 +12384,10 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M190" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="191">
@@ -12447,10 +12447,10 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M191" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="192">
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M192" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="193">
@@ -12573,10 +12573,10 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M193" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="194">
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M194" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="195">
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M195" t="n">
-        <v>34</v>
+        <v>45.94594594594595</v>
       </c>
     </row>
     <row r="196">
@@ -12762,10 +12762,10 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M196" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197">
@@ -12825,10 +12825,10 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M197" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="198">
@@ -12888,10 +12888,10 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M198" t="n">
-        <v>39</v>
+        <v>52.70270270270269</v>
       </c>
     </row>
     <row r="199">
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M199" t="n">
-        <v>19</v>
+        <v>25.67567567567567</v>
       </c>
     </row>
     <row r="200">
@@ -13014,10 +13014,10 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M200" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="201">
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M201" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="202">
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M202" t="n">
-        <v>13</v>
+        <v>17.56756756756757</v>
       </c>
     </row>
     <row r="203">
@@ -13203,10 +13203,10 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M203" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="204">
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M204" t="n">
-        <v>39</v>
+        <v>52.70270270270269</v>
       </c>
     </row>
     <row r="205">
@@ -13329,10 +13329,10 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M205" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="206">
@@ -13392,10 +13392,10 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M206" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="207">
@@ -13455,10 +13455,10 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M207" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="208">
@@ -13518,10 +13518,10 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M208" t="n">
-        <v>47</v>
+        <v>63.51351351351351</v>
       </c>
     </row>
     <row r="209">
@@ -13581,10 +13581,10 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M209" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="210">
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M210" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="211">
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M211" t="n">
-        <v>13</v>
+        <v>17.56756756756757</v>
       </c>
     </row>
     <row r="212">
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M212" t="n">
-        <v>43</v>
+        <v>58.10810810810811</v>
       </c>
     </row>
     <row r="213">
@@ -13833,10 +13833,10 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M213" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="214">
@@ -13896,10 +13896,10 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M214" t="n">
-        <v>65</v>
+        <v>87.83783783783784</v>
       </c>
     </row>
     <row r="215">
@@ -13959,10 +13959,10 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M215" t="n">
-        <v>25</v>
+        <v>33.78378378378378</v>
       </c>
     </row>
     <row r="216">
@@ -14022,10 +14022,10 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M216" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="217">
@@ -14085,10 +14085,10 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M217" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="218">
@@ -14148,10 +14148,10 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M218" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="219">
@@ -14211,10 +14211,10 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>18</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="M219" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="220">
@@ -14274,10 +14274,10 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M220" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="221">
@@ -14337,10 +14337,10 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M221" t="n">
-        <v>52</v>
+        <v>70.27027027027027</v>
       </c>
     </row>
     <row r="222">
@@ -14400,10 +14400,10 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M222" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="223">
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M223" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="224">
@@ -14526,10 +14526,10 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M224" t="n">
-        <v>33</v>
+        <v>44.5945945945946</v>
       </c>
     </row>
     <row r="225">
@@ -14589,10 +14589,10 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M225" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="226">
@@ -14652,10 +14652,10 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M226" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="227">
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M227" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="228">
@@ -14778,10 +14778,10 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M228" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="229">
@@ -14841,10 +14841,10 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M229" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="230">
@@ -14904,10 +14904,10 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M230" t="n">
-        <v>41</v>
+        <v>55.4054054054054</v>
       </c>
     </row>
     <row r="231">
@@ -14967,10 +14967,10 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M231" t="n">
-        <v>24</v>
+        <v>32.43243243243244</v>
       </c>
     </row>
     <row r="232">
@@ -15030,10 +15030,10 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M232" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="233">
@@ -15093,10 +15093,10 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M233" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="234">
@@ -15156,10 +15156,10 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M234" t="n">
-        <v>30</v>
+        <v>40.54054054054054</v>
       </c>
     </row>
     <row r="235">
@@ -15219,10 +15219,10 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M235" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="236">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M236" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="237">
@@ -15345,10 +15345,10 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M237" t="n">
-        <v>58</v>
+        <v>78.37837837837837</v>
       </c>
     </row>
     <row r="238">
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M238" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="239">
@@ -15471,10 +15471,10 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M239" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="240">
@@ -15534,10 +15534,10 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M240" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="241">
@@ -15597,10 +15597,10 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M241" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="242">
@@ -15660,10 +15660,10 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M242" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="243">
@@ -15723,10 +15723,10 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M243" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="244">
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M244" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="245">
@@ -15849,10 +15849,10 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M245" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="246">
@@ -15912,10 +15912,10 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M246" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="247">
@@ -15975,10 +15975,10 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M247" t="n">
-        <v>35</v>
+        <v>47.2972972972973</v>
       </c>
     </row>
     <row r="248">
@@ -16038,10 +16038,10 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M248" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="249">
@@ -16101,10 +16101,10 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M249" t="n">
-        <v>46</v>
+        <v>62.16216216216216</v>
       </c>
     </row>
     <row r="250">
@@ -16164,10 +16164,10 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M250" t="n">
-        <v>68</v>
+        <v>91.8918918918919</v>
       </c>
     </row>
     <row r="251">
@@ -16227,10 +16227,10 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M251" t="n">
-        <v>25</v>
+        <v>33.78378378378378</v>
       </c>
     </row>
     <row r="252">
@@ -16290,10 +16290,10 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M252" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="253">
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M253" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="254">
@@ -16416,10 +16416,10 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M254" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="255">
@@ -16479,10 +16479,10 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M255" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="256">
@@ -16542,10 +16542,10 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M256" t="n">
-        <v>11</v>
+        <v>14.86486486486486</v>
       </c>
     </row>
     <row r="257">
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="M257" t="n">
-        <v>3</v>
+        <v>4.054054054054054</v>
       </c>
     </row>
     <row r="258">
@@ -16668,10 +16668,10 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M258" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="259">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>18</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="M259" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="260">
@@ -16794,10 +16794,10 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M260" t="n">
-        <v>52</v>
+        <v>70.27027027027027</v>
       </c>
     </row>
     <row r="261">
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M261" t="n">
-        <v>46</v>
+        <v>62.16216216216216</v>
       </c>
     </row>
     <row r="262">
@@ -16920,10 +16920,10 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M262" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="263">
@@ -16983,10 +16983,10 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M263" t="n">
-        <v>45</v>
+        <v>60.81081081081081</v>
       </c>
     </row>
     <row r="264">
@@ -17046,10 +17046,10 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M264" t="n">
-        <v>32</v>
+        <v>43.24324324324324</v>
       </c>
     </row>
     <row r="265">
@@ -17109,10 +17109,10 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M265" t="n">
-        <v>26</v>
+        <v>35.13513513513514</v>
       </c>
     </row>
     <row r="266">
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M266" t="n">
-        <v>72</v>
+        <v>97.29729729729731</v>
       </c>
     </row>
     <row r="267">
@@ -17235,10 +17235,10 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M267" t="n">
-        <v>54</v>
+        <v>72.97297297297297</v>
       </c>
     </row>
     <row r="268">
@@ -17298,10 +17298,10 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>12</v>
+        <v>63.1578947368421</v>
       </c>
       <c r="M268" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="269">
@@ -17361,10 +17361,10 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M269" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="270">
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M270" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="271">
@@ -17487,10 +17487,10 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M271" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="272">
@@ -17550,10 +17550,10 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M272" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="273">
@@ -17613,10 +17613,10 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M273" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="274">
@@ -17676,10 +17676,10 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M274" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="275">
@@ -17739,10 +17739,10 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M275" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="276">
@@ -17802,10 +17802,10 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M276" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="277">
@@ -17865,10 +17865,10 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M277" t="n">
-        <v>49</v>
+        <v>66.21621621621621</v>
       </c>
     </row>
     <row r="278">
@@ -17928,10 +17928,10 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M278" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="279">
@@ -17991,10 +17991,10 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M279" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="280">
@@ -18054,10 +18054,10 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M280" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="281">
@@ -18117,10 +18117,10 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M281" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="282">
@@ -18180,10 +18180,10 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>17</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="M282" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="283">
@@ -18243,10 +18243,10 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M283" t="n">
-        <v>23</v>
+        <v>31.08108108108108</v>
       </c>
     </row>
     <row r="284">
@@ -18306,10 +18306,10 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M284" t="n">
-        <v>32</v>
+        <v>43.24324324324324</v>
       </c>
     </row>
     <row r="285">
@@ -18369,10 +18369,10 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M285" t="n">
-        <v>52</v>
+        <v>70.27027027027027</v>
       </c>
     </row>
     <row r="286">
@@ -18432,10 +18432,10 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M286" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="287">
@@ -18495,10 +18495,10 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M287" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="288">
@@ -18558,10 +18558,10 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>15</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="M288" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="289">
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>4</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M289" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="290">
@@ -18684,10 +18684,10 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M290" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="291">
@@ -18747,10 +18747,10 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M291" t="n">
-        <v>43</v>
+        <v>58.10810810810811</v>
       </c>
     </row>
     <row r="292">
@@ -18810,10 +18810,10 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M292" t="n">
-        <v>29</v>
+        <v>39.18918918918919</v>
       </c>
     </row>
     <row r="293">
@@ -18873,10 +18873,10 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M293" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="294">
@@ -18936,10 +18936,10 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M294" t="n">
-        <v>53</v>
+        <v>71.62162162162163</v>
       </c>
     </row>
     <row r="295">
@@ -18999,10 +18999,10 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>11</v>
+        <v>57.89473684210527</v>
       </c>
       <c r="M295" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="296">
@@ -19062,10 +19062,10 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M296" t="n">
-        <v>55</v>
+        <v>74.32432432432432</v>
       </c>
     </row>
     <row r="297">
@@ -19125,10 +19125,10 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M297" t="n">
-        <v>61</v>
+        <v>82.43243243243244</v>
       </c>
     </row>
     <row r="298">
@@ -19188,10 +19188,10 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M298" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="299">
@@ -19251,10 +19251,10 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>10</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="M299" t="n">
-        <v>52</v>
+        <v>70.27027027027027</v>
       </c>
     </row>
     <row r="300">
@@ -19314,10 +19314,10 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M300" t="n">
-        <v>38</v>
+        <v>51.35135135135135</v>
       </c>
     </row>
     <row r="301">
@@ -19377,10 +19377,10 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M301" t="n">
-        <v>39</v>
+        <v>52.70270270270269</v>
       </c>
     </row>
     <row r="302">
@@ -19440,10 +19440,10 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M302" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="303">
@@ -19503,10 +19503,10 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M303" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="304">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="M304" t="n">
-        <v>70</v>
+        <v>94.5945945945946</v>
       </c>
     </row>
     <row r="305">
@@ -19629,10 +19629,10 @@
         </is>
       </c>
       <c r="L305" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M305" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="306">
@@ -19692,10 +19692,10 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M306" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="307">
@@ -19755,10 +19755,10 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M307" t="n">
-        <v>57</v>
+        <v>77.02702702702703</v>
       </c>
     </row>
     <row r="308">
@@ -19818,10 +19818,10 @@
         </is>
       </c>
       <c r="L308" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M308" t="n">
-        <v>50</v>
+        <v>67.56756756756756</v>
       </c>
     </row>
     <row r="309">
@@ -19881,10 +19881,10 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M309" t="n">
-        <v>28</v>
+        <v>37.83783783783784</v>
       </c>
     </row>
     <row r="310">
@@ -19944,10 +19944,10 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>3</v>
+        <v>15.78947368421053</v>
       </c>
       <c r="M310" t="n">
-        <v>51</v>
+        <v>68.91891891891892</v>
       </c>
     </row>
     <row r="311">
@@ -20007,10 +20007,10 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>16</v>
+        <v>84.21052631578947</v>
       </c>
       <c r="M311" t="n">
-        <v>63</v>
+        <v>85.13513513513513</v>
       </c>
     </row>
     <row r="312">
@@ -20070,10 +20070,10 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M312" t="n">
-        <v>59</v>
+        <v>79.72972972972973</v>
       </c>
     </row>
     <row r="313">
@@ -20133,10 +20133,10 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M313" t="n">
-        <v>67</v>
+        <v>90.54054054054053</v>
       </c>
     </row>
     <row r="314">
@@ -20196,10 +20196,10 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M314" t="n">
-        <v>25</v>
+        <v>33.78378378378378</v>
       </c>
     </row>
     <row r="315">
@@ -20259,10 +20259,10 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M315" t="n">
-        <v>27</v>
+        <v>36.48648648648648</v>
       </c>
     </row>
     <row r="316">
@@ -20322,10 +20322,10 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>6</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="M316" t="n">
-        <v>66</v>
+        <v>89.18918918918919</v>
       </c>
     </row>
     <row r="317">
@@ -20385,10 +20385,10 @@
         </is>
       </c>
       <c r="L317" t="n">
-        <v>16</v>
+        <v>84.21052631578947</v>
       </c>
       <c r="M317" t="n">
-        <v>60</v>
+        <v>81.08108108108108</v>
       </c>
     </row>
     <row r="318">
@@ -20448,10 +20448,10 @@
         </is>
       </c>
       <c r="L318" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M318" t="n">
-        <v>69</v>
+        <v>93.24324324324324</v>
       </c>
     </row>
     <row r="319">
@@ -20511,10 +20511,10 @@
         </is>
       </c>
       <c r="L319" t="n">
-        <v>2</v>
+        <v>10.52631578947368</v>
       </c>
       <c r="M319" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
     <row r="320">
@@ -20574,10 +20574,10 @@
         </is>
       </c>
       <c r="L320" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M320" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="321">
@@ -20637,10 +20637,10 @@
         </is>
       </c>
       <c r="L321" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M321" t="n">
-        <v>65</v>
+        <v>87.83783783783784</v>
       </c>
     </row>
     <row r="322">
@@ -20700,10 +20700,10 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>13</v>
+        <v>68.42105263157895</v>
       </c>
       <c r="M322" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="323">
@@ -20763,10 +20763,10 @@
         </is>
       </c>
       <c r="L323" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M323" t="n">
-        <v>18</v>
+        <v>24.32432432432433</v>
       </c>
     </row>
     <row r="324">
@@ -20826,10 +20826,10 @@
         </is>
       </c>
       <c r="L324" t="n">
-        <v>7</v>
+        <v>36.84210526315789</v>
       </c>
       <c r="M324" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="325">
@@ -20889,10 +20889,10 @@
         </is>
       </c>
       <c r="L325" t="n">
-        <v>5</v>
+        <v>26.31578947368421</v>
       </c>
       <c r="M325" t="n">
-        <v>64</v>
+        <v>86.48648648648648</v>
       </c>
     </row>
     <row r="326">
@@ -20952,10 +20952,10 @@
         </is>
       </c>
       <c r="L326" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M326" t="n">
-        <v>21</v>
+        <v>28.37837837837838</v>
       </c>
     </row>
     <row r="327">
@@ -21015,10 +21015,10 @@
         </is>
       </c>
       <c r="L327" t="n">
-        <v>14</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="M327" t="n">
-        <v>62</v>
+        <v>83.78378378378379</v>
       </c>
     </row>
     <row r="328">
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="L328" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M328" t="n">
-        <v>34</v>
+        <v>45.94594594594595</v>
       </c>
     </row>
     <row r="329">
@@ -21141,10 +21141,10 @@
         </is>
       </c>
       <c r="L329" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M329" t="n">
-        <v>47</v>
+        <v>63.51351351351351</v>
       </c>
     </row>
     <row r="330">
@@ -21204,10 +21204,10 @@
         </is>
       </c>
       <c r="L330" t="n">
-        <v>8</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="M330" t="n">
-        <v>39</v>
+        <v>52.70270270270269</v>
       </c>
     </row>
     <row r="331">
@@ -21267,10 +21267,10 @@
         </is>
       </c>
       <c r="L331" t="n">
-        <v>9</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="M331" t="n">
-        <v>56</v>
+        <v>75.67567567567568</v>
       </c>
     </row>
   </sheetData>

--- a/output/df_padres_final.xlsx
+++ b/output/df_padres_final.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M331"/>
+  <dimension ref="A1:O331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,10 +474,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Indice_Conocimiento</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>Indice_Conocimiento_Norm</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Indice_Acompanamiento</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>Indice_Acompanamiento_Norm</t>
         </is>
@@ -540,9 +550,15 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M2" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>56</v>
+      </c>
+      <c r="O2" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -603,9 +619,15 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>59</v>
+      </c>
+      <c r="O3" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -666,9 +688,15 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>19</v>
+      </c>
+      <c r="M4" t="n">
         <v>100</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>65</v>
+      </c>
+      <c r="O4" t="n">
         <v>87.83783783783784</v>
       </c>
     </row>
@@ -729,9 +757,15 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>61</v>
+      </c>
+      <c r="O5" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -792,9 +826,15 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>67</v>
+      </c>
+      <c r="O6" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -855,9 +895,15 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>42</v>
+      </c>
+      <c r="O7" t="n">
         <v>56.75675675675676</v>
       </c>
     </row>
@@ -918,9 +964,15 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>27</v>
+      </c>
+      <c r="O8" t="n">
         <v>36.48648648648648</v>
       </c>
     </row>
@@ -981,9 +1033,15 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>18</v>
+      </c>
+      <c r="M9" t="n">
         <v>94.73684210526315</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>53</v>
+      </c>
+      <c r="O9" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -1044,9 +1102,15 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>66</v>
+      </c>
+      <c r="O10" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -1107,9 +1171,15 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>47</v>
+      </c>
+      <c r="O11" t="n">
         <v>63.51351351351351</v>
       </c>
     </row>
@@ -1170,9 +1240,15 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M12" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>47</v>
+      </c>
+      <c r="O12" t="n">
         <v>63.51351351351351</v>
       </c>
     </row>
@@ -1233,9 +1309,15 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>64</v>
+      </c>
+      <c r="O13" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -1296,9 +1378,15 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>59</v>
+      </c>
+      <c r="O14" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -1359,9 +1447,15 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>15</v>
+      </c>
+      <c r="M15" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>46</v>
+      </c>
+      <c r="O15" t="n">
         <v>62.16216216216216</v>
       </c>
     </row>
@@ -1422,9 +1516,15 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M16" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>54</v>
+      </c>
+      <c r="O16" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -1485,9 +1585,15 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>8</v>
+      </c>
+      <c r="M17" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>28</v>
+      </c>
+      <c r="O17" t="n">
         <v>37.83783783783784</v>
       </c>
     </row>
@@ -1548,9 +1654,15 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>58</v>
+      </c>
+      <c r="O18" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -1611,9 +1723,15 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>12</v>
+      </c>
+      <c r="M19" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>54</v>
+      </c>
+      <c r="O19" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -1674,9 +1792,15 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>57</v>
+      </c>
+      <c r="O20" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -1737,9 +1861,15 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>54</v>
+      </c>
+      <c r="O21" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -1800,9 +1930,15 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>13</v>
+      </c>
+      <c r="M22" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>60</v>
+      </c>
+      <c r="O22" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -1863,9 +1999,15 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>68</v>
+      </c>
+      <c r="O23" t="n">
         <v>91.8918918918919</v>
       </c>
     </row>
@@ -1926,9 +2068,15 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>19</v>
+      </c>
+      <c r="M24" t="n">
         <v>100</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
+        <v>56</v>
+      </c>
+      <c r="O24" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -1989,9 +2137,15 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>46</v>
+      </c>
+      <c r="O25" t="n">
         <v>62.16216216216216</v>
       </c>
     </row>
@@ -2052,9 +2206,15 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>9</v>
+      </c>
+      <c r="M26" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
+        <v>47</v>
+      </c>
+      <c r="O26" t="n">
         <v>63.51351351351351</v>
       </c>
     </row>
@@ -2115,9 +2275,15 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>8</v>
+      </c>
+      <c r="M27" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
+        <v>57</v>
+      </c>
+      <c r="O27" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -2178,9 +2344,15 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>9</v>
+      </c>
+      <c r="M28" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
+        <v>63</v>
+      </c>
+      <c r="O28" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -2241,9 +2413,15 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>12</v>
+      </c>
+      <c r="M29" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
+        <v>58</v>
+      </c>
+      <c r="O29" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -2304,9 +2482,15 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>14</v>
+      </c>
+      <c r="M30" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>48</v>
+      </c>
+      <c r="O30" t="n">
         <v>64.86486486486487</v>
       </c>
     </row>
@@ -2367,9 +2551,15 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>13</v>
+      </c>
+      <c r="M31" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>67</v>
+      </c>
+      <c r="O31" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -2430,9 +2620,15 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>14</v>
+      </c>
+      <c r="M32" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>66</v>
+      </c>
+      <c r="O32" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -2493,9 +2689,15 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>11</v>
+      </c>
+      <c r="M33" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
+        <v>56</v>
+      </c>
+      <c r="O33" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -2556,9 +2758,15 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>5</v>
+      </c>
+      <c r="M34" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>62</v>
+      </c>
+      <c r="O34" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -2619,9 +2827,15 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>16</v>
+      </c>
+      <c r="M35" t="n">
         <v>84.21052631578947</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
+        <v>61</v>
+      </c>
+      <c r="O35" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -2682,9 +2896,15 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>12</v>
+      </c>
+      <c r="M36" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
+        <v>67</v>
+      </c>
+      <c r="O36" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -2745,9 +2965,15 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
+        <v>60</v>
+      </c>
+      <c r="O37" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -2808,9 +3034,15 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>16</v>
+      </c>
+      <c r="M38" t="n">
         <v>84.21052631578947</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
+        <v>70</v>
+      </c>
+      <c r="O38" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -2871,9 +3103,15 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
+        <v>48</v>
+      </c>
+      <c r="O39" t="n">
         <v>64.86486486486487</v>
       </c>
     </row>
@@ -2934,9 +3172,15 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>12</v>
+      </c>
+      <c r="M40" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
+        <v>58</v>
+      </c>
+      <c r="O40" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -2997,9 +3241,15 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>14</v>
+      </c>
+      <c r="M41" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
+        <v>33</v>
+      </c>
+      <c r="O41" t="n">
         <v>44.5945945945946</v>
       </c>
     </row>
@@ -3060,9 +3310,15 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
+        <v>55</v>
+      </c>
+      <c r="O42" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -3123,9 +3379,15 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>9</v>
+      </c>
+      <c r="M43" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
+        <v>35</v>
+      </c>
+      <c r="O43" t="n">
         <v>47.2972972972973</v>
       </c>
     </row>
@@ -3186,9 +3448,15 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>12</v>
+      </c>
+      <c r="M44" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
+        <v>51</v>
+      </c>
+      <c r="O44" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -3249,9 +3517,15 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>11</v>
+      </c>
+      <c r="M45" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
+        <v>65</v>
+      </c>
+      <c r="O45" t="n">
         <v>87.83783783783784</v>
       </c>
     </row>
@@ -3312,9 +3586,15 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
+        <v>62</v>
+      </c>
+      <c r="O46" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -3375,9 +3655,15 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>14</v>
+      </c>
+      <c r="M47" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
+        <v>60</v>
+      </c>
+      <c r="O47" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -3438,9 +3724,15 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
+        <v>49</v>
+      </c>
+      <c r="O48" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -3501,9 +3793,15 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>17</v>
+      </c>
+      <c r="M49" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
+        <v>73</v>
+      </c>
+      <c r="O49" t="n">
         <v>98.64864864864865</v>
       </c>
     </row>
@@ -3564,9 +3862,15 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>19</v>
+      </c>
+      <c r="M50" t="n">
         <v>100</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
+        <v>73</v>
+      </c>
+      <c r="O50" t="n">
         <v>98.64864864864865</v>
       </c>
     </row>
@@ -3627,9 +3931,15 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>9</v>
+      </c>
+      <c r="M51" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
+        <v>51</v>
+      </c>
+      <c r="O51" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -3690,9 +4000,15 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>12</v>
+      </c>
+      <c r="M52" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
+        <v>57</v>
+      </c>
+      <c r="O52" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -3753,9 +4069,15 @@
         </is>
       </c>
       <c r="L53" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
+        <v>50</v>
+      </c>
+      <c r="O53" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -3816,9 +4138,15 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>8</v>
+      </c>
+      <c r="M54" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
+        <v>37</v>
+      </c>
+      <c r="O54" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3879,9 +4207,15 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>13</v>
+      </c>
+      <c r="M55" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
+        <v>48</v>
+      </c>
+      <c r="O55" t="n">
         <v>64.86486486486487</v>
       </c>
     </row>
@@ -3942,9 +4276,15 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>19</v>
+      </c>
+      <c r="M56" t="n">
         <v>100</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
+        <v>51</v>
+      </c>
+      <c r="O56" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -4005,9 +4345,15 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>9</v>
+      </c>
+      <c r="M57" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
+        <v>67</v>
+      </c>
+      <c r="O57" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -4068,9 +4414,15 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>7</v>
+      </c>
+      <c r="M58" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
+        <v>44</v>
+      </c>
+      <c r="O58" t="n">
         <v>59.45945945945946</v>
       </c>
     </row>
@@ -4131,9 +4483,15 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>19</v>
+      </c>
+      <c r="M59" t="n">
         <v>100</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
+        <v>53</v>
+      </c>
+      <c r="O59" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -4194,9 +4552,15 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>14</v>
+      </c>
+      <c r="M60" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
+        <v>58</v>
+      </c>
+      <c r="O60" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -4257,9 +4621,15 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>6</v>
+      </c>
+      <c r="M61" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
+        <v>33</v>
+      </c>
+      <c r="O61" t="n">
         <v>44.5945945945946</v>
       </c>
     </row>
@@ -4320,9 +4690,15 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>13</v>
+      </c>
+      <c r="M62" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
+        <v>61</v>
+      </c>
+      <c r="O62" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -4383,9 +4759,15 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>8</v>
+      </c>
+      <c r="M63" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
+        <v>54</v>
+      </c>
+      <c r="O63" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -4446,9 +4828,15 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>14</v>
+      </c>
+      <c r="M64" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
+        <v>59</v>
+      </c>
+      <c r="O64" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -4509,9 +4897,15 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>4</v>
+      </c>
+      <c r="M65" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
+        <v>31</v>
+      </c>
+      <c r="O65" t="n">
         <v>41.89189189189189</v>
       </c>
     </row>
@@ -4572,9 +4966,15 @@
         </is>
       </c>
       <c r="L66" t="n">
+        <v>6</v>
+      </c>
+      <c r="M66" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
+        <v>32</v>
+      </c>
+      <c r="O66" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -4635,9 +5035,15 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>8</v>
+      </c>
+      <c r="M67" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
+        <v>42</v>
+      </c>
+      <c r="O67" t="n">
         <v>56.75675675675676</v>
       </c>
     </row>
@@ -4698,9 +5104,15 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>4</v>
+      </c>
+      <c r="M68" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
+        <v>49</v>
+      </c>
+      <c r="O68" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -4761,9 +5173,15 @@
         </is>
       </c>
       <c r="L69" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
+        <v>43</v>
+      </c>
+      <c r="O69" t="n">
         <v>58.10810810810811</v>
       </c>
     </row>
@@ -4824,9 +5242,15 @@
         </is>
       </c>
       <c r="L70" t="n">
+        <v>14</v>
+      </c>
+      <c r="M70" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
+        <v>58</v>
+      </c>
+      <c r="O70" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -4887,9 +5311,15 @@
         </is>
       </c>
       <c r="L71" t="n">
+        <v>14</v>
+      </c>
+      <c r="M71" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
+        <v>70</v>
+      </c>
+      <c r="O71" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -4950,9 +5380,15 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>8</v>
+      </c>
+      <c r="M72" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
+        <v>31</v>
+      </c>
+      <c r="O72" t="n">
         <v>41.89189189189189</v>
       </c>
     </row>
@@ -5013,9 +5449,15 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>17</v>
+      </c>
+      <c r="M73" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
+        <v>63</v>
+      </c>
+      <c r="O73" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -5076,9 +5518,15 @@
         </is>
       </c>
       <c r="L74" t="n">
+        <v>8</v>
+      </c>
+      <c r="M74" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
+        <v>74</v>
+      </c>
+      <c r="O74" t="n">
         <v>100</v>
       </c>
     </row>
@@ -5139,9 +5587,15 @@
         </is>
       </c>
       <c r="L75" t="n">
+        <v>9</v>
+      </c>
+      <c r="M75" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
+        <v>69</v>
+      </c>
+      <c r="O75" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -5202,9 +5656,15 @@
         </is>
       </c>
       <c r="L76" t="n">
+        <v>7</v>
+      </c>
+      <c r="M76" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
+        <v>49</v>
+      </c>
+      <c r="O76" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -5265,9 +5725,15 @@
         </is>
       </c>
       <c r="L77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M77" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
+        <v>54</v>
+      </c>
+      <c r="O77" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -5328,9 +5794,15 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>10</v>
+      </c>
+      <c r="M78" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
+        <v>62</v>
+      </c>
+      <c r="O78" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -5391,9 +5863,15 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>6</v>
+      </c>
+      <c r="M79" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
+        <v>31</v>
+      </c>
+      <c r="O79" t="n">
         <v>41.89189189189189</v>
       </c>
     </row>
@@ -5454,9 +5932,15 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
         <v>5.263157894736842</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
         <v>1.351351351351351</v>
       </c>
     </row>
@@ -5517,9 +6001,15 @@
         </is>
       </c>
       <c r="L81" t="n">
+        <v>8</v>
+      </c>
+      <c r="M81" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
+        <v>68</v>
+      </c>
+      <c r="O81" t="n">
         <v>91.8918918918919</v>
       </c>
     </row>
@@ -5580,9 +6070,15 @@
         </is>
       </c>
       <c r="L82" t="n">
+        <v>7</v>
+      </c>
+      <c r="M82" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
+        <v>63</v>
+      </c>
+      <c r="O82" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -5643,9 +6139,15 @@
         </is>
       </c>
       <c r="L83" t="n">
+        <v>8</v>
+      </c>
+      <c r="M83" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
+        <v>29</v>
+      </c>
+      <c r="O83" t="n">
         <v>39.18918918918919</v>
       </c>
     </row>
@@ -5706,9 +6208,15 @@
         </is>
       </c>
       <c r="L84" t="n">
+        <v>9</v>
+      </c>
+      <c r="M84" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
+        <v>51</v>
+      </c>
+      <c r="O84" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -5769,9 +6277,15 @@
         </is>
       </c>
       <c r="L85" t="n">
+        <v>4</v>
+      </c>
+      <c r="M85" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
+        <v>32</v>
+      </c>
+      <c r="O85" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -5832,9 +6346,15 @@
         </is>
       </c>
       <c r="L86" t="n">
+        <v>8</v>
+      </c>
+      <c r="M86" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
+        <v>23</v>
+      </c>
+      <c r="O86" t="n">
         <v>31.08108108108108</v>
       </c>
     </row>
@@ -5895,9 +6415,15 @@
         </is>
       </c>
       <c r="L87" t="n">
+        <v>9</v>
+      </c>
+      <c r="M87" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
+        <v>53</v>
+      </c>
+      <c r="O87" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -5958,9 +6484,15 @@
         </is>
       </c>
       <c r="L88" t="n">
+        <v>5</v>
+      </c>
+      <c r="M88" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
+        <v>17</v>
+      </c>
+      <c r="O88" t="n">
         <v>22.97297297297298</v>
       </c>
     </row>
@@ -6021,9 +6553,15 @@
         </is>
       </c>
       <c r="L89" t="n">
+        <v>8</v>
+      </c>
+      <c r="M89" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M89" t="n">
+      <c r="N89" t="n">
+        <v>60</v>
+      </c>
+      <c r="O89" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -6084,9 +6622,15 @@
         </is>
       </c>
       <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M90" t="n">
+      <c r="N90" t="n">
+        <v>55</v>
+      </c>
+      <c r="O90" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -6147,9 +6691,15 @@
         </is>
       </c>
       <c r="L91" t="n">
+        <v>6</v>
+      </c>
+      <c r="M91" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M91" t="n">
+      <c r="N91" t="n">
+        <v>28</v>
+      </c>
+      <c r="O91" t="n">
         <v>37.83783783783784</v>
       </c>
     </row>
@@ -6210,9 +6760,15 @@
         </is>
       </c>
       <c r="L92" t="n">
+        <v>6</v>
+      </c>
+      <c r="M92" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
+        <v>40</v>
+      </c>
+      <c r="O92" t="n">
         <v>54.05405405405406</v>
       </c>
     </row>
@@ -6273,9 +6829,15 @@
         </is>
       </c>
       <c r="L93" t="n">
+        <v>6</v>
+      </c>
+      <c r="M93" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
+        <v>54</v>
+      </c>
+      <c r="O93" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -6336,9 +6898,15 @@
         </is>
       </c>
       <c r="L94" t="n">
+        <v>6</v>
+      </c>
+      <c r="M94" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
+        <v>43</v>
+      </c>
+      <c r="O94" t="n">
         <v>58.10810810810811</v>
       </c>
     </row>
@@ -6399,9 +6967,15 @@
         </is>
       </c>
       <c r="L95" t="n">
+        <v>11</v>
+      </c>
+      <c r="M95" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M95" t="n">
+      <c r="N95" t="n">
+        <v>33</v>
+      </c>
+      <c r="O95" t="n">
         <v>44.5945945945946</v>
       </c>
     </row>
@@ -6462,9 +7036,15 @@
         </is>
       </c>
       <c r="L96" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M96" t="n">
+      <c r="N96" t="n">
+        <v>56</v>
+      </c>
+      <c r="O96" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -6525,9 +7105,15 @@
         </is>
       </c>
       <c r="L97" t="n">
+        <v>4</v>
+      </c>
+      <c r="M97" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
+        <v>69</v>
+      </c>
+      <c r="O97" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -6588,9 +7174,15 @@
         </is>
       </c>
       <c r="L98" t="n">
+        <v>17</v>
+      </c>
+      <c r="M98" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M98" t="n">
+      <c r="N98" t="n">
+        <v>65</v>
+      </c>
+      <c r="O98" t="n">
         <v>87.83783783783784</v>
       </c>
     </row>
@@ -6651,9 +7243,15 @@
         </is>
       </c>
       <c r="L99" t="n">
+        <v>5</v>
+      </c>
+      <c r="M99" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M99" t="n">
+      <c r="N99" t="n">
+        <v>56</v>
+      </c>
+      <c r="O99" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -6714,9 +7312,15 @@
         </is>
       </c>
       <c r="L100" t="n">
+        <v>7</v>
+      </c>
+      <c r="M100" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M100" t="n">
+      <c r="N100" t="n">
+        <v>61</v>
+      </c>
+      <c r="O100" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -6777,9 +7381,15 @@
         </is>
       </c>
       <c r="L101" t="n">
+        <v>7</v>
+      </c>
+      <c r="M101" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M101" t="n">
+      <c r="N101" t="n">
+        <v>60</v>
+      </c>
+      <c r="O101" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -6840,9 +7450,15 @@
         </is>
       </c>
       <c r="L102" t="n">
+        <v>12</v>
+      </c>
+      <c r="M102" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M102" t="n">
+      <c r="N102" t="n">
+        <v>38</v>
+      </c>
+      <c r="O102" t="n">
         <v>51.35135135135135</v>
       </c>
     </row>
@@ -6903,9 +7519,15 @@
         </is>
       </c>
       <c r="L103" t="n">
+        <v>13</v>
+      </c>
+      <c r="M103" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M103" t="n">
+      <c r="N103" t="n">
+        <v>58</v>
+      </c>
+      <c r="O103" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -6966,9 +7588,15 @@
         </is>
       </c>
       <c r="L104" t="n">
+        <v>5</v>
+      </c>
+      <c r="M104" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M104" t="n">
+      <c r="N104" t="n">
+        <v>59</v>
+      </c>
+      <c r="O104" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -7029,9 +7657,15 @@
         </is>
       </c>
       <c r="L105" t="n">
+        <v>3</v>
+      </c>
+      <c r="M105" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M105" t="n">
+      <c r="N105" t="n">
+        <v>65</v>
+      </c>
+      <c r="O105" t="n">
         <v>87.83783783783784</v>
       </c>
     </row>
@@ -7092,9 +7726,15 @@
         </is>
       </c>
       <c r="L106" t="n">
+        <v>8</v>
+      </c>
+      <c r="M106" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M106" t="n">
+      <c r="N106" t="n">
+        <v>55</v>
+      </c>
+      <c r="O106" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -7155,9 +7795,15 @@
         </is>
       </c>
       <c r="L107" t="n">
+        <v>10</v>
+      </c>
+      <c r="M107" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M107" t="n">
+      <c r="N107" t="n">
+        <v>62</v>
+      </c>
+      <c r="O107" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -7218,9 +7864,15 @@
         </is>
       </c>
       <c r="L108" t="n">
+        <v>9</v>
+      </c>
+      <c r="M108" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M108" t="n">
+      <c r="N108" t="n">
+        <v>66</v>
+      </c>
+      <c r="O108" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -7281,9 +7933,15 @@
         </is>
       </c>
       <c r="L109" t="n">
+        <v>8</v>
+      </c>
+      <c r="M109" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M109" t="n">
+      <c r="N109" t="n">
+        <v>59</v>
+      </c>
+      <c r="O109" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -7344,9 +8002,15 @@
         </is>
       </c>
       <c r="L110" t="n">
+        <v>8</v>
+      </c>
+      <c r="M110" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M110" t="n">
+      <c r="N110" t="n">
+        <v>38</v>
+      </c>
+      <c r="O110" t="n">
         <v>51.35135135135135</v>
       </c>
     </row>
@@ -7407,9 +8071,15 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>10</v>
+      </c>
+      <c r="M111" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M111" t="n">
+      <c r="N111" t="n">
+        <v>50</v>
+      </c>
+      <c r="O111" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -7470,9 +8140,15 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>9</v>
+      </c>
+      <c r="M112" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M112" t="n">
+      <c r="N112" t="n">
+        <v>66</v>
+      </c>
+      <c r="O112" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -7533,9 +8209,15 @@
         </is>
       </c>
       <c r="L113" t="n">
+        <v>14</v>
+      </c>
+      <c r="M113" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M113" t="n">
+      <c r="N113" t="n">
+        <v>62</v>
+      </c>
+      <c r="O113" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -7596,9 +8278,15 @@
         </is>
       </c>
       <c r="L114" t="n">
+        <v>8</v>
+      </c>
+      <c r="M114" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M114" t="n">
+      <c r="N114" t="n">
+        <v>53</v>
+      </c>
+      <c r="O114" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -7659,9 +8347,15 @@
         </is>
       </c>
       <c r="L115" t="n">
+        <v>9</v>
+      </c>
+      <c r="M115" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M115" t="n">
+      <c r="N115" t="n">
+        <v>19</v>
+      </c>
+      <c r="O115" t="n">
         <v>25.67567567567567</v>
       </c>
     </row>
@@ -7722,9 +8416,15 @@
         </is>
       </c>
       <c r="L116" t="n">
+        <v>7</v>
+      </c>
+      <c r="M116" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M116" t="n">
+      <c r="N116" t="n">
+        <v>56</v>
+      </c>
+      <c r="O116" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -7785,9 +8485,15 @@
         </is>
       </c>
       <c r="L117" t="n">
+        <v>15</v>
+      </c>
+      <c r="M117" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M117" t="n">
+      <c r="N117" t="n">
+        <v>62</v>
+      </c>
+      <c r="O117" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -7848,9 +8554,15 @@
         </is>
       </c>
       <c r="L118" t="n">
+        <v>12</v>
+      </c>
+      <c r="M118" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M118" t="n">
+      <c r="N118" t="n">
+        <v>74</v>
+      </c>
+      <c r="O118" t="n">
         <v>100</v>
       </c>
     </row>
@@ -7911,9 +8623,15 @@
         </is>
       </c>
       <c r="L119" t="n">
+        <v>14</v>
+      </c>
+      <c r="M119" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M119" t="n">
+      <c r="N119" t="n">
+        <v>54</v>
+      </c>
+      <c r="O119" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -7974,9 +8692,15 @@
         </is>
       </c>
       <c r="L120" t="n">
+        <v>4</v>
+      </c>
+      <c r="M120" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M120" t="n">
+      <c r="N120" t="n">
+        <v>61</v>
+      </c>
+      <c r="O120" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -8037,9 +8761,15 @@
         </is>
       </c>
       <c r="L121" t="n">
+        <v>7</v>
+      </c>
+      <c r="M121" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M121" t="n">
+      <c r="N121" t="n">
+        <v>45</v>
+      </c>
+      <c r="O121" t="n">
         <v>60.81081081081081</v>
       </c>
     </row>
@@ -8100,9 +8830,15 @@
         </is>
       </c>
       <c r="L122" t="n">
+        <v>6</v>
+      </c>
+      <c r="M122" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M122" t="n">
+      <c r="N122" t="n">
+        <v>29</v>
+      </c>
+      <c r="O122" t="n">
         <v>39.18918918918919</v>
       </c>
     </row>
@@ -8163,9 +8899,15 @@
         </is>
       </c>
       <c r="L123" t="n">
+        <v>9</v>
+      </c>
+      <c r="M123" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M123" t="n">
+      <c r="N123" t="n">
+        <v>32</v>
+      </c>
+      <c r="O123" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -8226,9 +8968,15 @@
         </is>
       </c>
       <c r="L124" t="n">
+        <v>16</v>
+      </c>
+      <c r="M124" t="n">
         <v>84.21052631578947</v>
       </c>
-      <c r="M124" t="n">
+      <c r="N124" t="n">
+        <v>54</v>
+      </c>
+      <c r="O124" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -8289,9 +9037,15 @@
         </is>
       </c>
       <c r="L125" t="n">
+        <v>3</v>
+      </c>
+      <c r="M125" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M125" t="n">
+      <c r="N125" t="n">
+        <v>43</v>
+      </c>
+      <c r="O125" t="n">
         <v>58.10810810810811</v>
       </c>
     </row>
@@ -8352,9 +9106,15 @@
         </is>
       </c>
       <c r="L126" t="n">
+        <v>5</v>
+      </c>
+      <c r="M126" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M126" t="n">
+      <c r="N126" t="n">
+        <v>70</v>
+      </c>
+      <c r="O126" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -8415,9 +9175,15 @@
         </is>
       </c>
       <c r="L127" t="n">
+        <v>9</v>
+      </c>
+      <c r="M127" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M127" t="n">
+      <c r="N127" t="n">
+        <v>67</v>
+      </c>
+      <c r="O127" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -8478,9 +9244,15 @@
         </is>
       </c>
       <c r="L128" t="n">
+        <v>14</v>
+      </c>
+      <c r="M128" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M128" t="n">
+      <c r="N128" t="n">
+        <v>54</v>
+      </c>
+      <c r="O128" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -8541,9 +9313,15 @@
         </is>
       </c>
       <c r="L129" t="n">
+        <v>8</v>
+      </c>
+      <c r="M129" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M129" t="n">
+      <c r="N129" t="n">
+        <v>58</v>
+      </c>
+      <c r="O129" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -8604,9 +9382,15 @@
         </is>
       </c>
       <c r="L130" t="n">
+        <v>5</v>
+      </c>
+      <c r="M130" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M130" t="n">
+      <c r="N130" t="n">
+        <v>35</v>
+      </c>
+      <c r="O130" t="n">
         <v>47.2972972972973</v>
       </c>
     </row>
@@ -8667,9 +9451,15 @@
         </is>
       </c>
       <c r="L131" t="n">
+        <v>12</v>
+      </c>
+      <c r="M131" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M131" t="n">
+      <c r="N131" t="n">
+        <v>45</v>
+      </c>
+      <c r="O131" t="n">
         <v>60.81081081081081</v>
       </c>
     </row>
@@ -8730,9 +9520,15 @@
         </is>
       </c>
       <c r="L132" t="n">
+        <v>4</v>
+      </c>
+      <c r="M132" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M132" t="n">
+      <c r="N132" t="n">
+        <v>12</v>
+      </c>
+      <c r="O132" t="n">
         <v>16.21621621621622</v>
       </c>
     </row>
@@ -8793,9 +9589,15 @@
         </is>
       </c>
       <c r="L133" t="n">
+        <v>4</v>
+      </c>
+      <c r="M133" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M133" t="n">
+      <c r="N133" t="n">
+        <v>25</v>
+      </c>
+      <c r="O133" t="n">
         <v>33.78378378378378</v>
       </c>
     </row>
@@ -8856,9 +9658,15 @@
         </is>
       </c>
       <c r="L134" t="n">
+        <v>6</v>
+      </c>
+      <c r="M134" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M134" t="n">
+      <c r="N134" t="n">
+        <v>26</v>
+      </c>
+      <c r="O134" t="n">
         <v>35.13513513513514</v>
       </c>
     </row>
@@ -8919,9 +9727,15 @@
         </is>
       </c>
       <c r="L135" t="n">
+        <v>3</v>
+      </c>
+      <c r="M135" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M135" t="n">
+      <c r="N135" t="n">
+        <v>40</v>
+      </c>
+      <c r="O135" t="n">
         <v>54.05405405405406</v>
       </c>
     </row>
@@ -8982,9 +9796,15 @@
         </is>
       </c>
       <c r="L136" t="n">
+        <v>12</v>
+      </c>
+      <c r="M136" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M136" t="n">
+      <c r="N136" t="n">
+        <v>37</v>
+      </c>
+      <c r="O136" t="n">
         <v>50</v>
       </c>
     </row>
@@ -9045,9 +9865,15 @@
         </is>
       </c>
       <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
         <v>5.263157894736842</v>
       </c>
-      <c r="M137" t="n">
+      <c r="N137" t="n">
+        <v>20</v>
+      </c>
+      <c r="O137" t="n">
         <v>27.02702702702703</v>
       </c>
     </row>
@@ -9108,9 +9934,15 @@
         </is>
       </c>
       <c r="L138" t="n">
+        <v>7</v>
+      </c>
+      <c r="M138" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M138" t="n">
+      <c r="N138" t="n">
+        <v>27</v>
+      </c>
+      <c r="O138" t="n">
         <v>36.48648648648648</v>
       </c>
     </row>
@@ -9171,9 +10003,15 @@
         </is>
       </c>
       <c r="L139" t="n">
+        <v>9</v>
+      </c>
+      <c r="M139" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M139" t="n">
+      <c r="N139" t="n">
+        <v>36</v>
+      </c>
+      <c r="O139" t="n">
         <v>48.64864864864865</v>
       </c>
     </row>
@@ -9234,9 +10072,15 @@
         </is>
       </c>
       <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
         <v>5.263157894736842</v>
       </c>
-      <c r="M140" t="n">
+      <c r="N140" t="n">
+        <v>37</v>
+      </c>
+      <c r="O140" t="n">
         <v>50</v>
       </c>
     </row>
@@ -9297,9 +10141,15 @@
         </is>
       </c>
       <c r="L141" t="n">
+        <v>13</v>
+      </c>
+      <c r="M141" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M141" t="n">
+      <c r="N141" t="n">
+        <v>64</v>
+      </c>
+      <c r="O141" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -9360,9 +10210,15 @@
         </is>
       </c>
       <c r="L142" t="n">
+        <v>7</v>
+      </c>
+      <c r="M142" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M142" t="n">
+      <c r="N142" t="n">
+        <v>57</v>
+      </c>
+      <c r="O142" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -9423,9 +10279,15 @@
         </is>
       </c>
       <c r="L143" t="n">
+        <v>9</v>
+      </c>
+      <c r="M143" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M143" t="n">
+      <c r="N143" t="n">
+        <v>45</v>
+      </c>
+      <c r="O143" t="n">
         <v>60.81081081081081</v>
       </c>
     </row>
@@ -9486,9 +10348,15 @@
         </is>
       </c>
       <c r="L144" t="n">
+        <v>9</v>
+      </c>
+      <c r="M144" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M144" t="n">
+      <c r="N144" t="n">
+        <v>48</v>
+      </c>
+      <c r="O144" t="n">
         <v>64.86486486486487</v>
       </c>
     </row>
@@ -9549,9 +10417,15 @@
         </is>
       </c>
       <c r="L145" t="n">
+        <v>18</v>
+      </c>
+      <c r="M145" t="n">
         <v>94.73684210526315</v>
       </c>
-      <c r="M145" t="n">
+      <c r="N145" t="n">
+        <v>69</v>
+      </c>
+      <c r="O145" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -9612,9 +10486,15 @@
         </is>
       </c>
       <c r="L146" t="n">
+        <v>7</v>
+      </c>
+      <c r="M146" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M146" t="n">
+      <c r="N146" t="n">
+        <v>63</v>
+      </c>
+      <c r="O146" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -9675,9 +10555,15 @@
         </is>
       </c>
       <c r="L147" t="n">
+        <v>9</v>
+      </c>
+      <c r="M147" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M147" t="n">
+      <c r="N147" t="n">
+        <v>70</v>
+      </c>
+      <c r="O147" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -9738,9 +10624,15 @@
         </is>
       </c>
       <c r="L148" t="n">
+        <v>18</v>
+      </c>
+      <c r="M148" t="n">
         <v>94.73684210526315</v>
       </c>
-      <c r="M148" t="n">
+      <c r="N148" t="n">
+        <v>63</v>
+      </c>
+      <c r="O148" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -9801,9 +10693,15 @@
         </is>
       </c>
       <c r="L149" t="n">
+        <v>8</v>
+      </c>
+      <c r="M149" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M149" t="n">
+      <c r="N149" t="n">
+        <v>58</v>
+      </c>
+      <c r="O149" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -9864,9 +10762,15 @@
         </is>
       </c>
       <c r="L150" t="n">
+        <v>9</v>
+      </c>
+      <c r="M150" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M150" t="n">
+      <c r="N150" t="n">
+        <v>39</v>
+      </c>
+      <c r="O150" t="n">
         <v>52.70270270270269</v>
       </c>
     </row>
@@ -9927,9 +10831,15 @@
         </is>
       </c>
       <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M151" t="n">
+      <c r="N151" t="n">
+        <v>74</v>
+      </c>
+      <c r="O151" t="n">
         <v>100</v>
       </c>
     </row>
@@ -9990,9 +10900,15 @@
         </is>
       </c>
       <c r="L152" t="n">
+        <v>4</v>
+      </c>
+      <c r="M152" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M152" t="n">
+      <c r="N152" t="n">
+        <v>74</v>
+      </c>
+      <c r="O152" t="n">
         <v>100</v>
       </c>
     </row>
@@ -10053,9 +10969,15 @@
         </is>
       </c>
       <c r="L153" t="n">
+        <v>9</v>
+      </c>
+      <c r="M153" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M153" t="n">
+      <c r="N153" t="n">
+        <v>60</v>
+      </c>
+      <c r="O153" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -10116,9 +11038,15 @@
         </is>
       </c>
       <c r="L154" t="n">
+        <v>9</v>
+      </c>
+      <c r="M154" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M154" t="n">
+      <c r="N154" t="n">
+        <v>59</v>
+      </c>
+      <c r="O154" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -10179,9 +11107,15 @@
         </is>
       </c>
       <c r="L155" t="n">
+        <v>5</v>
+      </c>
+      <c r="M155" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M155" t="n">
+      <c r="N155" t="n">
+        <v>53</v>
+      </c>
+      <c r="O155" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -10242,9 +11176,15 @@
         </is>
       </c>
       <c r="L156" t="n">
+        <v>10</v>
+      </c>
+      <c r="M156" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M156" t="n">
+      <c r="N156" t="n">
+        <v>60</v>
+      </c>
+      <c r="O156" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -10305,9 +11245,15 @@
         </is>
       </c>
       <c r="L157" t="n">
+        <v>2</v>
+      </c>
+      <c r="M157" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M157" t="n">
+      <c r="N157" t="n">
+        <v>32</v>
+      </c>
+      <c r="O157" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -10368,9 +11314,15 @@
         </is>
       </c>
       <c r="L158" t="n">
+        <v>2</v>
+      </c>
+      <c r="M158" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M158" t="n">
+      <c r="N158" t="n">
+        <v>34</v>
+      </c>
+      <c r="O158" t="n">
         <v>45.94594594594595</v>
       </c>
     </row>
@@ -10431,9 +11383,15 @@
         </is>
       </c>
       <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M159" t="n">
+      <c r="N159" t="n">
+        <v>48</v>
+      </c>
+      <c r="O159" t="n">
         <v>64.86486486486487</v>
       </c>
     </row>
@@ -10494,9 +11452,15 @@
         </is>
       </c>
       <c r="L160" t="n">
+        <v>6</v>
+      </c>
+      <c r="M160" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M160" t="n">
+      <c r="N160" t="n">
+        <v>61</v>
+      </c>
+      <c r="O160" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -10557,9 +11521,15 @@
         </is>
       </c>
       <c r="L161" t="n">
+        <v>8</v>
+      </c>
+      <c r="M161" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M161" t="n">
+      <c r="N161" t="n">
+        <v>50</v>
+      </c>
+      <c r="O161" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -10620,9 +11590,15 @@
         </is>
       </c>
       <c r="L162" t="n">
+        <v>13</v>
+      </c>
+      <c r="M162" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M162" t="n">
+      <c r="N162" t="n">
+        <v>68</v>
+      </c>
+      <c r="O162" t="n">
         <v>91.8918918918919</v>
       </c>
     </row>
@@ -10683,9 +11659,15 @@
         </is>
       </c>
       <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M163" t="n">
+      <c r="N163" t="n">
+        <v>40</v>
+      </c>
+      <c r="O163" t="n">
         <v>54.05405405405406</v>
       </c>
     </row>
@@ -10746,9 +11728,15 @@
         </is>
       </c>
       <c r="L164" t="n">
+        <v>6</v>
+      </c>
+      <c r="M164" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M164" t="n">
+      <c r="N164" t="n">
+        <v>7</v>
+      </c>
+      <c r="O164" t="n">
         <v>9.45945945945946</v>
       </c>
     </row>
@@ -10809,9 +11797,15 @@
         </is>
       </c>
       <c r="L165" t="n">
+        <v>10</v>
+      </c>
+      <c r="M165" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M165" t="n">
+      <c r="N165" t="n">
+        <v>61</v>
+      </c>
+      <c r="O165" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -10872,9 +11866,15 @@
         </is>
       </c>
       <c r="L166" t="n">
+        <v>6</v>
+      </c>
+      <c r="M166" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M166" t="n">
+      <c r="N166" t="n">
+        <v>48</v>
+      </c>
+      <c r="O166" t="n">
         <v>64.86486486486487</v>
       </c>
     </row>
@@ -10935,9 +11935,15 @@
         </is>
       </c>
       <c r="L167" t="n">
+        <v>14</v>
+      </c>
+      <c r="M167" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M167" t="n">
+      <c r="N167" t="n">
+        <v>55</v>
+      </c>
+      <c r="O167" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -10998,9 +12004,15 @@
         </is>
       </c>
       <c r="L168" t="n">
+        <v>7</v>
+      </c>
+      <c r="M168" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M168" t="n">
+      <c r="N168" t="n">
+        <v>49</v>
+      </c>
+      <c r="O168" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -11061,9 +12073,15 @@
         </is>
       </c>
       <c r="L169" t="n">
+        <v>4</v>
+      </c>
+      <c r="M169" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M169" t="n">
+      <c r="N169" t="n">
+        <v>39</v>
+      </c>
+      <c r="O169" t="n">
         <v>52.70270270270269</v>
       </c>
     </row>
@@ -11124,9 +12142,15 @@
         </is>
       </c>
       <c r="L170" t="n">
+        <v>4</v>
+      </c>
+      <c r="M170" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M170" t="n">
+      <c r="N170" t="n">
+        <v>15</v>
+      </c>
+      <c r="O170" t="n">
         <v>20.27027027027027</v>
       </c>
     </row>
@@ -11187,9 +12211,15 @@
         </is>
       </c>
       <c r="L171" t="n">
+        <v>7</v>
+      </c>
+      <c r="M171" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M171" t="n">
+      <c r="N171" t="n">
+        <v>46</v>
+      </c>
+      <c r="O171" t="n">
         <v>62.16216216216216</v>
       </c>
     </row>
@@ -11250,9 +12280,15 @@
         </is>
       </c>
       <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
         <v>5.263157894736842</v>
       </c>
-      <c r="M172" t="n">
+      <c r="N172" t="n">
+        <v>34</v>
+      </c>
+      <c r="O172" t="n">
         <v>45.94594594594595</v>
       </c>
     </row>
@@ -11313,9 +12349,15 @@
         </is>
       </c>
       <c r="L173" t="n">
+        <v>2</v>
+      </c>
+      <c r="M173" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M173" t="n">
+      <c r="N173" t="n">
+        <v>56</v>
+      </c>
+      <c r="O173" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -11376,9 +12418,15 @@
         </is>
       </c>
       <c r="L174" t="n">
+        <v>12</v>
+      </c>
+      <c r="M174" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M174" t="n">
+      <c r="N174" t="n">
+        <v>57</v>
+      </c>
+      <c r="O174" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -11439,9 +12487,15 @@
         </is>
       </c>
       <c r="L175" t="n">
+        <v>4</v>
+      </c>
+      <c r="M175" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M175" t="n">
+      <c r="N175" t="n">
+        <v>18</v>
+      </c>
+      <c r="O175" t="n">
         <v>24.32432432432433</v>
       </c>
     </row>
@@ -11502,9 +12556,15 @@
         </is>
       </c>
       <c r="L176" t="n">
+        <v>9</v>
+      </c>
+      <c r="M176" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M176" t="n">
+      <c r="N176" t="n">
+        <v>67</v>
+      </c>
+      <c r="O176" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -11565,9 +12625,15 @@
         </is>
       </c>
       <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
         <v>5.263157894736842</v>
       </c>
-      <c r="M177" t="n">
+      <c r="N177" t="n">
+        <v>6</v>
+      </c>
+      <c r="O177" t="n">
         <v>8.108108108108109</v>
       </c>
     </row>
@@ -11628,9 +12694,15 @@
         </is>
       </c>
       <c r="L178" t="n">
+        <v>14</v>
+      </c>
+      <c r="M178" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M178" t="n">
+      <c r="N178" t="n">
+        <v>28</v>
+      </c>
+      <c r="O178" t="n">
         <v>37.83783783783784</v>
       </c>
     </row>
@@ -11691,9 +12763,15 @@
         </is>
       </c>
       <c r="L179" t="n">
+        <v>7</v>
+      </c>
+      <c r="M179" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M179" t="n">
+      <c r="N179" t="n">
+        <v>66</v>
+      </c>
+      <c r="O179" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -11754,9 +12832,15 @@
         </is>
       </c>
       <c r="L180" t="n">
+        <v>8</v>
+      </c>
+      <c r="M180" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M180" t="n">
+      <c r="N180" t="n">
+        <v>27</v>
+      </c>
+      <c r="O180" t="n">
         <v>36.48648648648648</v>
       </c>
     </row>
@@ -11817,9 +12901,15 @@
         </is>
       </c>
       <c r="L181" t="n">
+        <v>4</v>
+      </c>
+      <c r="M181" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M181" t="n">
+      <c r="N181" t="n">
+        <v>54</v>
+      </c>
+      <c r="O181" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -11880,9 +12970,15 @@
         </is>
       </c>
       <c r="L182" t="n">
+        <v>8</v>
+      </c>
+      <c r="M182" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M182" t="n">
+      <c r="N182" t="n">
+        <v>62</v>
+      </c>
+      <c r="O182" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -11943,9 +13039,15 @@
         </is>
       </c>
       <c r="L183" t="n">
+        <v>17</v>
+      </c>
+      <c r="M183" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M183" t="n">
+      <c r="N183" t="n">
+        <v>66</v>
+      </c>
+      <c r="O183" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -12006,9 +13108,15 @@
         </is>
       </c>
       <c r="L184" t="n">
+        <v>7</v>
+      </c>
+      <c r="M184" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M184" t="n">
+      <c r="N184" t="n">
+        <v>56</v>
+      </c>
+      <c r="O184" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -12069,9 +13177,15 @@
         </is>
       </c>
       <c r="L185" t="n">
+        <v>7</v>
+      </c>
+      <c r="M185" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M185" t="n">
+      <c r="N185" t="n">
+        <v>74</v>
+      </c>
+      <c r="O185" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12132,9 +13246,15 @@
         </is>
       </c>
       <c r="L186" t="n">
+        <v>13</v>
+      </c>
+      <c r="M186" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M186" t="n">
+      <c r="N186" t="n">
+        <v>29</v>
+      </c>
+      <c r="O186" t="n">
         <v>39.18918918918919</v>
       </c>
     </row>
@@ -12195,9 +13315,15 @@
         </is>
       </c>
       <c r="L187" t="n">
+        <v>6</v>
+      </c>
+      <c r="M187" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M187" t="n">
+      <c r="N187" t="n">
+        <v>46</v>
+      </c>
+      <c r="O187" t="n">
         <v>62.16216216216216</v>
       </c>
     </row>
@@ -12258,9 +13384,15 @@
         </is>
       </c>
       <c r="L188" t="n">
+        <v>8</v>
+      </c>
+      <c r="M188" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M188" t="n">
+      <c r="N188" t="n">
+        <v>70</v>
+      </c>
+      <c r="O188" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -12321,9 +13453,15 @@
         </is>
       </c>
       <c r="L189" t="n">
+        <v>10</v>
+      </c>
+      <c r="M189" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M189" t="n">
+      <c r="N189" t="n">
+        <v>54</v>
+      </c>
+      <c r="O189" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -12384,9 +13522,15 @@
         </is>
       </c>
       <c r="L190" t="n">
+        <v>9</v>
+      </c>
+      <c r="M190" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M190" t="n">
+      <c r="N190" t="n">
+        <v>63</v>
+      </c>
+      <c r="O190" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -12447,9 +13591,15 @@
         </is>
       </c>
       <c r="L191" t="n">
+        <v>9</v>
+      </c>
+      <c r="M191" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M191" t="n">
+      <c r="N191" t="n">
+        <v>50</v>
+      </c>
+      <c r="O191" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -12510,9 +13660,15 @@
         </is>
       </c>
       <c r="L192" t="n">
+        <v>9</v>
+      </c>
+      <c r="M192" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M192" t="n">
+      <c r="N192" t="n">
+        <v>57</v>
+      </c>
+      <c r="O192" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -12573,9 +13729,15 @@
         </is>
       </c>
       <c r="L193" t="n">
+        <v>17</v>
+      </c>
+      <c r="M193" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M193" t="n">
+      <c r="N193" t="n">
+        <v>70</v>
+      </c>
+      <c r="O193" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -12636,9 +13798,15 @@
         </is>
       </c>
       <c r="L194" t="n">
+        <v>6</v>
+      </c>
+      <c r="M194" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M194" t="n">
+      <c r="N194" t="n">
+        <v>66</v>
+      </c>
+      <c r="O194" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -12699,9 +13867,15 @@
         </is>
       </c>
       <c r="L195" t="n">
+        <v>9</v>
+      </c>
+      <c r="M195" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M195" t="n">
+      <c r="N195" t="n">
+        <v>34</v>
+      </c>
+      <c r="O195" t="n">
         <v>45.94594594594595</v>
       </c>
     </row>
@@ -12762,9 +13936,15 @@
         </is>
       </c>
       <c r="L196" t="n">
+        <v>7</v>
+      </c>
+      <c r="M196" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M196" t="n">
+      <c r="N196" t="n">
+        <v>74</v>
+      </c>
+      <c r="O196" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12825,9 +14005,15 @@
         </is>
       </c>
       <c r="L197" t="n">
+        <v>8</v>
+      </c>
+      <c r="M197" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M197" t="n">
+      <c r="N197" t="n">
+        <v>74</v>
+      </c>
+      <c r="O197" t="n">
         <v>100</v>
       </c>
     </row>
@@ -12888,9 +14074,15 @@
         </is>
       </c>
       <c r="L198" t="n">
+        <v>8</v>
+      </c>
+      <c r="M198" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M198" t="n">
+      <c r="N198" t="n">
+        <v>39</v>
+      </c>
+      <c r="O198" t="n">
         <v>52.70270270270269</v>
       </c>
     </row>
@@ -12951,9 +14143,15 @@
         </is>
       </c>
       <c r="L199" t="n">
+        <v>2</v>
+      </c>
+      <c r="M199" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M199" t="n">
+      <c r="N199" t="n">
+        <v>19</v>
+      </c>
+      <c r="O199" t="n">
         <v>25.67567567567567</v>
       </c>
     </row>
@@ -13014,9 +14212,15 @@
         </is>
       </c>
       <c r="L200" t="n">
+        <v>11</v>
+      </c>
+      <c r="M200" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M200" t="n">
+      <c r="N200" t="n">
+        <v>58</v>
+      </c>
+      <c r="O200" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -13077,9 +14281,15 @@
         </is>
       </c>
       <c r="L201" t="n">
+        <v>15</v>
+      </c>
+      <c r="M201" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M201" t="n">
+      <c r="N201" t="n">
+        <v>64</v>
+      </c>
+      <c r="O201" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -13140,9 +14350,15 @@
         </is>
       </c>
       <c r="L202" t="n">
+        <v>2</v>
+      </c>
+      <c r="M202" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M202" t="n">
+      <c r="N202" t="n">
+        <v>13</v>
+      </c>
+      <c r="O202" t="n">
         <v>17.56756756756757</v>
       </c>
     </row>
@@ -13203,9 +14419,15 @@
         </is>
       </c>
       <c r="L203" t="n">
+        <v>8</v>
+      </c>
+      <c r="M203" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M203" t="n">
+      <c r="N203" t="n">
+        <v>66</v>
+      </c>
+      <c r="O203" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -13266,9 +14488,15 @@
         </is>
       </c>
       <c r="L204" t="n">
+        <v>10</v>
+      </c>
+      <c r="M204" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M204" t="n">
+      <c r="N204" t="n">
+        <v>39</v>
+      </c>
+      <c r="O204" t="n">
         <v>52.70270270270269</v>
       </c>
     </row>
@@ -13329,9 +14557,15 @@
         </is>
       </c>
       <c r="L205" t="n">
+        <v>9</v>
+      </c>
+      <c r="M205" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M205" t="n">
+      <c r="N205" t="n">
+        <v>60</v>
+      </c>
+      <c r="O205" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -13392,9 +14626,15 @@
         </is>
       </c>
       <c r="L206" t="n">
+        <v>8</v>
+      </c>
+      <c r="M206" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M206" t="n">
+      <c r="N206" t="n">
+        <v>63</v>
+      </c>
+      <c r="O206" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -13455,9 +14695,15 @@
         </is>
       </c>
       <c r="L207" t="n">
+        <v>7</v>
+      </c>
+      <c r="M207" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M207" t="n">
+      <c r="N207" t="n">
+        <v>67</v>
+      </c>
+      <c r="O207" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -13518,9 +14764,15 @@
         </is>
       </c>
       <c r="L208" t="n">
+        <v>9</v>
+      </c>
+      <c r="M208" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M208" t="n">
+      <c r="N208" t="n">
+        <v>47</v>
+      </c>
+      <c r="O208" t="n">
         <v>63.51351351351351</v>
       </c>
     </row>
@@ -13581,9 +14833,15 @@
         </is>
       </c>
       <c r="L209" t="n">
+        <v>7</v>
+      </c>
+      <c r="M209" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M209" t="n">
+      <c r="N209" t="n">
+        <v>53</v>
+      </c>
+      <c r="O209" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -13644,9 +14902,15 @@
         </is>
       </c>
       <c r="L210" t="n">
+        <v>5</v>
+      </c>
+      <c r="M210" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M210" t="n">
+      <c r="N210" t="n">
+        <v>59</v>
+      </c>
+      <c r="O210" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -13707,9 +14971,15 @@
         </is>
       </c>
       <c r="L211" t="n">
+        <v>9</v>
+      </c>
+      <c r="M211" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M211" t="n">
+      <c r="N211" t="n">
+        <v>13</v>
+      </c>
+      <c r="O211" t="n">
         <v>17.56756756756757</v>
       </c>
     </row>
@@ -13770,9 +15040,15 @@
         </is>
       </c>
       <c r="L212" t="n">
+        <v>6</v>
+      </c>
+      <c r="M212" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M212" t="n">
+      <c r="N212" t="n">
+        <v>43</v>
+      </c>
+      <c r="O212" t="n">
         <v>58.10810810810811</v>
       </c>
     </row>
@@ -13833,9 +15109,15 @@
         </is>
       </c>
       <c r="L213" t="n">
+        <v>19</v>
+      </c>
+      <c r="M213" t="n">
         <v>100</v>
       </c>
-      <c r="M213" t="n">
+      <c r="N213" t="n">
+        <v>60</v>
+      </c>
+      <c r="O213" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -13896,9 +15178,15 @@
         </is>
       </c>
       <c r="L214" t="n">
+        <v>4</v>
+      </c>
+      <c r="M214" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M214" t="n">
+      <c r="N214" t="n">
+        <v>65</v>
+      </c>
+      <c r="O214" t="n">
         <v>87.83783783783784</v>
       </c>
     </row>
@@ -13959,9 +15247,15 @@
         </is>
       </c>
       <c r="L215" t="n">
+        <v>9</v>
+      </c>
+      <c r="M215" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M215" t="n">
+      <c r="N215" t="n">
+        <v>25</v>
+      </c>
+      <c r="O215" t="n">
         <v>33.78378378378378</v>
       </c>
     </row>
@@ -14022,9 +15316,15 @@
         </is>
       </c>
       <c r="L216" t="n">
+        <v>4</v>
+      </c>
+      <c r="M216" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M216" t="n">
+      <c r="N216" t="n">
+        <v>57</v>
+      </c>
+      <c r="O216" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -14085,9 +15385,15 @@
         </is>
       </c>
       <c r="L217" t="n">
+        <v>6</v>
+      </c>
+      <c r="M217" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M217" t="n">
+      <c r="N217" t="n">
+        <v>57</v>
+      </c>
+      <c r="O217" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -14148,9 +15454,15 @@
         </is>
       </c>
       <c r="L218" t="n">
+        <v>8</v>
+      </c>
+      <c r="M218" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M218" t="n">
+      <c r="N218" t="n">
+        <v>50</v>
+      </c>
+      <c r="O218" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -14211,9 +15523,15 @@
         </is>
       </c>
       <c r="L219" t="n">
+        <v>18</v>
+      </c>
+      <c r="M219" t="n">
         <v>94.73684210526315</v>
       </c>
-      <c r="M219" t="n">
+      <c r="N219" t="n">
+        <v>63</v>
+      </c>
+      <c r="O219" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -14274,9 +15592,15 @@
         </is>
       </c>
       <c r="L220" t="n">
+        <v>2</v>
+      </c>
+      <c r="M220" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M220" t="n">
+      <c r="N220" t="n">
+        <v>37</v>
+      </c>
+      <c r="O220" t="n">
         <v>50</v>
       </c>
     </row>
@@ -14337,9 +15661,15 @@
         </is>
       </c>
       <c r="L221" t="n">
+        <v>9</v>
+      </c>
+      <c r="M221" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M221" t="n">
+      <c r="N221" t="n">
+        <v>52</v>
+      </c>
+      <c r="O221" t="n">
         <v>70.27027027027027</v>
       </c>
     </row>
@@ -14400,9 +15730,15 @@
         </is>
       </c>
       <c r="L222" t="n">
+        <v>10</v>
+      </c>
+      <c r="M222" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M222" t="n">
+      <c r="N222" t="n">
+        <v>74</v>
+      </c>
+      <c r="O222" t="n">
         <v>100</v>
       </c>
     </row>
@@ -14463,9 +15799,15 @@
         </is>
       </c>
       <c r="L223" t="n">
+        <v>4</v>
+      </c>
+      <c r="M223" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M223" t="n">
+      <c r="N223" t="n">
+        <v>59</v>
+      </c>
+      <c r="O223" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -14526,9 +15868,15 @@
         </is>
       </c>
       <c r="L224" t="n">
+        <v>2</v>
+      </c>
+      <c r="M224" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M224" t="n">
+      <c r="N224" t="n">
+        <v>33</v>
+      </c>
+      <c r="O224" t="n">
         <v>44.5945945945946</v>
       </c>
     </row>
@@ -14589,9 +15937,15 @@
         </is>
       </c>
       <c r="L225" t="n">
+        <v>19</v>
+      </c>
+      <c r="M225" t="n">
         <v>100</v>
       </c>
-      <c r="M225" t="n">
+      <c r="N225" t="n">
+        <v>61</v>
+      </c>
+      <c r="O225" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -14652,9 +16006,15 @@
         </is>
       </c>
       <c r="L226" t="n">
+        <v>6</v>
+      </c>
+      <c r="M226" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M226" t="n">
+      <c r="N226" t="n">
+        <v>51</v>
+      </c>
+      <c r="O226" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -14715,9 +16075,15 @@
         </is>
       </c>
       <c r="L227" t="n">
+        <v>14</v>
+      </c>
+      <c r="M227" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M227" t="n">
+      <c r="N227" t="n">
+        <v>51</v>
+      </c>
+      <c r="O227" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -14778,9 +16144,15 @@
         </is>
       </c>
       <c r="L228" t="n">
+        <v>4</v>
+      </c>
+      <c r="M228" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M228" t="n">
+      <c r="N228" t="n">
+        <v>49</v>
+      </c>
+      <c r="O228" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -14841,9 +16213,15 @@
         </is>
       </c>
       <c r="L229" t="n">
+        <v>5</v>
+      </c>
+      <c r="M229" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M229" t="n">
+      <c r="N229" t="n">
+        <v>55</v>
+      </c>
+      <c r="O229" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -14904,9 +16282,15 @@
         </is>
       </c>
       <c r="L230" t="n">
+        <v>9</v>
+      </c>
+      <c r="M230" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M230" t="n">
+      <c r="N230" t="n">
+        <v>41</v>
+      </c>
+      <c r="O230" t="n">
         <v>55.4054054054054</v>
       </c>
     </row>
@@ -14967,9 +16351,15 @@
         </is>
       </c>
       <c r="L231" t="n">
+        <v>9</v>
+      </c>
+      <c r="M231" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M231" t="n">
+      <c r="N231" t="n">
+        <v>24</v>
+      </c>
+      <c r="O231" t="n">
         <v>32.43243243243244</v>
       </c>
     </row>
@@ -15030,9 +16420,15 @@
         </is>
       </c>
       <c r="L232" t="n">
+        <v>7</v>
+      </c>
+      <c r="M232" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M232" t="n">
+      <c r="N232" t="n">
+        <v>53</v>
+      </c>
+      <c r="O232" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -15093,9 +16489,15 @@
         </is>
       </c>
       <c r="L233" t="n">
+        <v>8</v>
+      </c>
+      <c r="M233" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M233" t="n">
+      <c r="N233" t="n">
+        <v>51</v>
+      </c>
+      <c r="O233" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -15156,9 +16558,15 @@
         </is>
       </c>
       <c r="L234" t="n">
+        <v>13</v>
+      </c>
+      <c r="M234" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M234" t="n">
+      <c r="N234" t="n">
+        <v>30</v>
+      </c>
+      <c r="O234" t="n">
         <v>40.54054054054054</v>
       </c>
     </row>
@@ -15219,9 +16627,15 @@
         </is>
       </c>
       <c r="L235" t="n">
+        <v>9</v>
+      </c>
+      <c r="M235" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M235" t="n">
+      <c r="N235" t="n">
+        <v>60</v>
+      </c>
+      <c r="O235" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -15282,9 +16696,15 @@
         </is>
       </c>
       <c r="L236" t="n">
+        <v>9</v>
+      </c>
+      <c r="M236" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M236" t="n">
+      <c r="N236" t="n">
+        <v>56</v>
+      </c>
+      <c r="O236" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -15345,9 +16765,15 @@
         </is>
       </c>
       <c r="L237" t="n">
+        <v>3</v>
+      </c>
+      <c r="M237" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M237" t="n">
+      <c r="N237" t="n">
+        <v>58</v>
+      </c>
+      <c r="O237" t="n">
         <v>78.37837837837837</v>
       </c>
     </row>
@@ -15408,9 +16834,15 @@
         </is>
       </c>
       <c r="L238" t="n">
+        <v>3</v>
+      </c>
+      <c r="M238" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M238" t="n">
+      <c r="N238" t="n">
+        <v>49</v>
+      </c>
+      <c r="O238" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -15471,9 +16903,15 @@
         </is>
       </c>
       <c r="L239" t="n">
+        <v>13</v>
+      </c>
+      <c r="M239" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M239" t="n">
+      <c r="N239" t="n">
+        <v>62</v>
+      </c>
+      <c r="O239" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -15534,9 +16972,15 @@
         </is>
       </c>
       <c r="L240" t="n">
+        <v>11</v>
+      </c>
+      <c r="M240" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M240" t="n">
+      <c r="N240" t="n">
+        <v>62</v>
+      </c>
+      <c r="O240" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -15597,9 +17041,15 @@
         </is>
       </c>
       <c r="L241" t="n">
+        <v>6</v>
+      </c>
+      <c r="M241" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M241" t="n">
+      <c r="N241" t="n">
+        <v>67</v>
+      </c>
+      <c r="O241" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -15660,9 +17110,15 @@
         </is>
       </c>
       <c r="L242" t="n">
+        <v>15</v>
+      </c>
+      <c r="M242" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M242" t="n">
+      <c r="N242" t="n">
+        <v>69</v>
+      </c>
+      <c r="O242" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -15723,9 +17179,15 @@
         </is>
       </c>
       <c r="L243" t="n">
+        <v>8</v>
+      </c>
+      <c r="M243" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M243" t="n">
+      <c r="N243" t="n">
+        <v>60</v>
+      </c>
+      <c r="O243" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -15786,9 +17248,15 @@
         </is>
       </c>
       <c r="L244" t="n">
+        <v>14</v>
+      </c>
+      <c r="M244" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M244" t="n">
+      <c r="N244" t="n">
+        <v>61</v>
+      </c>
+      <c r="O244" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -15849,9 +17317,15 @@
         </is>
       </c>
       <c r="L245" t="n">
+        <v>12</v>
+      </c>
+      <c r="M245" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M245" t="n">
+      <c r="N245" t="n">
+        <v>66</v>
+      </c>
+      <c r="O245" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -15912,9 +17386,15 @@
         </is>
       </c>
       <c r="L246" t="n">
+        <v>6</v>
+      </c>
+      <c r="M246" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M246" t="n">
+      <c r="N246" t="n">
+        <v>51</v>
+      </c>
+      <c r="O246" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -15975,9 +17455,15 @@
         </is>
       </c>
       <c r="L247" t="n">
+        <v>2</v>
+      </c>
+      <c r="M247" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M247" t="n">
+      <c r="N247" t="n">
+        <v>35</v>
+      </c>
+      <c r="O247" t="n">
         <v>47.2972972972973</v>
       </c>
     </row>
@@ -16038,9 +17524,15 @@
         </is>
       </c>
       <c r="L248" t="n">
+        <v>15</v>
+      </c>
+      <c r="M248" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M248" t="n">
+      <c r="N248" t="n">
+        <v>62</v>
+      </c>
+      <c r="O248" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -16101,9 +17593,15 @@
         </is>
       </c>
       <c r="L249" t="n">
+        <v>5</v>
+      </c>
+      <c r="M249" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M249" t="n">
+      <c r="N249" t="n">
+        <v>46</v>
+      </c>
+      <c r="O249" t="n">
         <v>62.16216216216216</v>
       </c>
     </row>
@@ -16164,9 +17662,15 @@
         </is>
       </c>
       <c r="L250" t="n">
+        <v>2</v>
+      </c>
+      <c r="M250" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M250" t="n">
+      <c r="N250" t="n">
+        <v>68</v>
+      </c>
+      <c r="O250" t="n">
         <v>91.8918918918919</v>
       </c>
     </row>
@@ -16227,9 +17731,15 @@
         </is>
       </c>
       <c r="L251" t="n">
+        <v>10</v>
+      </c>
+      <c r="M251" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M251" t="n">
+      <c r="N251" t="n">
+        <v>25</v>
+      </c>
+      <c r="O251" t="n">
         <v>33.78378378378378</v>
       </c>
     </row>
@@ -16290,9 +17800,15 @@
         </is>
       </c>
       <c r="L252" t="n">
+        <v>7</v>
+      </c>
+      <c r="M252" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M252" t="n">
+      <c r="N252" t="n">
+        <v>56</v>
+      </c>
+      <c r="O252" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -16353,9 +17869,15 @@
         </is>
       </c>
       <c r="L253" t="n">
+        <v>2</v>
+      </c>
+      <c r="M253" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M253" t="n">
+      <c r="N253" t="n">
+        <v>62</v>
+      </c>
+      <c r="O253" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -16416,9 +17938,15 @@
         </is>
       </c>
       <c r="L254" t="n">
+        <v>17</v>
+      </c>
+      <c r="M254" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M254" t="n">
+      <c r="N254" t="n">
+        <v>74</v>
+      </c>
+      <c r="O254" t="n">
         <v>100</v>
       </c>
     </row>
@@ -16479,9 +18007,15 @@
         </is>
       </c>
       <c r="L255" t="n">
+        <v>5</v>
+      </c>
+      <c r="M255" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M255" t="n">
+      <c r="N255" t="n">
+        <v>53</v>
+      </c>
+      <c r="O255" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -16542,9 +18076,15 @@
         </is>
       </c>
       <c r="L256" t="n">
+        <v>5</v>
+      </c>
+      <c r="M256" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M256" t="n">
+      <c r="N256" t="n">
+        <v>11</v>
+      </c>
+      <c r="O256" t="n">
         <v>14.86486486486486</v>
       </c>
     </row>
@@ -16605,9 +18145,15 @@
         </is>
       </c>
       <c r="L257" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" t="n">
         <v>5.263157894736842</v>
       </c>
-      <c r="M257" t="n">
+      <c r="N257" t="n">
+        <v>3</v>
+      </c>
+      <c r="O257" t="n">
         <v>4.054054054054054</v>
       </c>
     </row>
@@ -16668,9 +18214,15 @@
         </is>
       </c>
       <c r="L258" t="n">
+        <v>6</v>
+      </c>
+      <c r="M258" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M258" t="n">
+      <c r="N258" t="n">
+        <v>66</v>
+      </c>
+      <c r="O258" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -16731,9 +18283,15 @@
         </is>
       </c>
       <c r="L259" t="n">
+        <v>18</v>
+      </c>
+      <c r="M259" t="n">
         <v>94.73684210526315</v>
       </c>
-      <c r="M259" t="n">
+      <c r="N259" t="n">
+        <v>74</v>
+      </c>
+      <c r="O259" t="n">
         <v>100</v>
       </c>
     </row>
@@ -16794,9 +18352,15 @@
         </is>
       </c>
       <c r="L260" t="n">
+        <v>11</v>
+      </c>
+      <c r="M260" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M260" t="n">
+      <c r="N260" t="n">
+        <v>52</v>
+      </c>
+      <c r="O260" t="n">
         <v>70.27027027027027</v>
       </c>
     </row>
@@ -16857,9 +18421,15 @@
         </is>
       </c>
       <c r="L261" t="n">
+        <v>2</v>
+      </c>
+      <c r="M261" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M261" t="n">
+      <c r="N261" t="n">
+        <v>46</v>
+      </c>
+      <c r="O261" t="n">
         <v>62.16216216216216</v>
       </c>
     </row>
@@ -16920,9 +18490,15 @@
         </is>
       </c>
       <c r="L262" t="n">
+        <v>8</v>
+      </c>
+      <c r="M262" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M262" t="n">
+      <c r="N262" t="n">
+        <v>59</v>
+      </c>
+      <c r="O262" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -16983,9 +18559,15 @@
         </is>
       </c>
       <c r="L263" t="n">
+        <v>9</v>
+      </c>
+      <c r="M263" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M263" t="n">
+      <c r="N263" t="n">
+        <v>45</v>
+      </c>
+      <c r="O263" t="n">
         <v>60.81081081081081</v>
       </c>
     </row>
@@ -17046,9 +18628,15 @@
         </is>
       </c>
       <c r="L264" t="n">
+        <v>13</v>
+      </c>
+      <c r="M264" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M264" t="n">
+      <c r="N264" t="n">
+        <v>32</v>
+      </c>
+      <c r="O264" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -17109,9 +18697,15 @@
         </is>
       </c>
       <c r="L265" t="n">
+        <v>4</v>
+      </c>
+      <c r="M265" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M265" t="n">
+      <c r="N265" t="n">
+        <v>26</v>
+      </c>
+      <c r="O265" t="n">
         <v>35.13513513513514</v>
       </c>
     </row>
@@ -17172,9 +18766,15 @@
         </is>
       </c>
       <c r="L266" t="n">
+        <v>6</v>
+      </c>
+      <c r="M266" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M266" t="n">
+      <c r="N266" t="n">
+        <v>72</v>
+      </c>
+      <c r="O266" t="n">
         <v>97.29729729729731</v>
       </c>
     </row>
@@ -17235,9 +18835,15 @@
         </is>
       </c>
       <c r="L267" t="n">
+        <v>8</v>
+      </c>
+      <c r="M267" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M267" t="n">
+      <c r="N267" t="n">
+        <v>54</v>
+      </c>
+      <c r="O267" t="n">
         <v>72.97297297297297</v>
       </c>
     </row>
@@ -17298,9 +18904,15 @@
         </is>
       </c>
       <c r="L268" t="n">
+        <v>12</v>
+      </c>
+      <c r="M268" t="n">
         <v>63.1578947368421</v>
       </c>
-      <c r="M268" t="n">
+      <c r="N268" t="n">
+        <v>53</v>
+      </c>
+      <c r="O268" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -17361,9 +18973,15 @@
         </is>
       </c>
       <c r="L269" t="n">
+        <v>9</v>
+      </c>
+      <c r="M269" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M269" t="n">
+      <c r="N269" t="n">
+        <v>55</v>
+      </c>
+      <c r="O269" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -17424,9 +19042,15 @@
         </is>
       </c>
       <c r="L270" t="n">
+        <v>8</v>
+      </c>
+      <c r="M270" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M270" t="n">
+      <c r="N270" t="n">
+        <v>50</v>
+      </c>
+      <c r="O270" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -17487,9 +19111,15 @@
         </is>
       </c>
       <c r="L271" t="n">
+        <v>6</v>
+      </c>
+      <c r="M271" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M271" t="n">
+      <c r="N271" t="n">
+        <v>66</v>
+      </c>
+      <c r="O271" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -17550,9 +19180,15 @@
         </is>
       </c>
       <c r="L272" t="n">
+        <v>7</v>
+      </c>
+      <c r="M272" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M272" t="n">
+      <c r="N272" t="n">
+        <v>50</v>
+      </c>
+      <c r="O272" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -17613,9 +19249,15 @@
         </is>
       </c>
       <c r="L273" t="n">
+        <v>15</v>
+      </c>
+      <c r="M273" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M273" t="n">
+      <c r="N273" t="n">
+        <v>55</v>
+      </c>
+      <c r="O273" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -17676,9 +19318,15 @@
         </is>
       </c>
       <c r="L274" t="n">
+        <v>9</v>
+      </c>
+      <c r="M274" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M274" t="n">
+      <c r="N274" t="n">
+        <v>55</v>
+      </c>
+      <c r="O274" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -17739,9 +19387,15 @@
         </is>
       </c>
       <c r="L275" t="n">
+        <v>8</v>
+      </c>
+      <c r="M275" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M275" t="n">
+      <c r="N275" t="n">
+        <v>57</v>
+      </c>
+      <c r="O275" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -17802,9 +19456,15 @@
         </is>
       </c>
       <c r="L276" t="n">
+        <v>10</v>
+      </c>
+      <c r="M276" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M276" t="n">
+      <c r="N276" t="n">
+        <v>67</v>
+      </c>
+      <c r="O276" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -17865,9 +19525,15 @@
         </is>
       </c>
       <c r="L277" t="n">
+        <v>8</v>
+      </c>
+      <c r="M277" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M277" t="n">
+      <c r="N277" t="n">
+        <v>49</v>
+      </c>
+      <c r="O277" t="n">
         <v>66.21621621621621</v>
       </c>
     </row>
@@ -17928,9 +19594,15 @@
         </is>
       </c>
       <c r="L278" t="n">
+        <v>7</v>
+      </c>
+      <c r="M278" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M278" t="n">
+      <c r="N278" t="n">
+        <v>53</v>
+      </c>
+      <c r="O278" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -17991,9 +19663,15 @@
         </is>
       </c>
       <c r="L279" t="n">
+        <v>9</v>
+      </c>
+      <c r="M279" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M279" t="n">
+      <c r="N279" t="n">
+        <v>66</v>
+      </c>
+      <c r="O279" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -18054,9 +19732,15 @@
         </is>
       </c>
       <c r="L280" t="n">
+        <v>9</v>
+      </c>
+      <c r="M280" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M280" t="n">
+      <c r="N280" t="n">
+        <v>51</v>
+      </c>
+      <c r="O280" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -18117,9 +19801,15 @@
         </is>
       </c>
       <c r="L281" t="n">
+        <v>9</v>
+      </c>
+      <c r="M281" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M281" t="n">
+      <c r="N281" t="n">
+        <v>56</v>
+      </c>
+      <c r="O281" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -18180,9 +19870,15 @@
         </is>
       </c>
       <c r="L282" t="n">
+        <v>17</v>
+      </c>
+      <c r="M282" t="n">
         <v>89.47368421052632</v>
       </c>
-      <c r="M282" t="n">
+      <c r="N282" t="n">
+        <v>69</v>
+      </c>
+      <c r="O282" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -18243,9 +19939,15 @@
         </is>
       </c>
       <c r="L283" t="n">
+        <v>13</v>
+      </c>
+      <c r="M283" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M283" t="n">
+      <c r="N283" t="n">
+        <v>23</v>
+      </c>
+      <c r="O283" t="n">
         <v>31.08108108108108</v>
       </c>
     </row>
@@ -18306,9 +20008,15 @@
         </is>
       </c>
       <c r="L284" t="n">
+        <v>9</v>
+      </c>
+      <c r="M284" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M284" t="n">
+      <c r="N284" t="n">
+        <v>32</v>
+      </c>
+      <c r="O284" t="n">
         <v>43.24324324324324</v>
       </c>
     </row>
@@ -18369,9 +20077,15 @@
         </is>
       </c>
       <c r="L285" t="n">
+        <v>9</v>
+      </c>
+      <c r="M285" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M285" t="n">
+      <c r="N285" t="n">
+        <v>52</v>
+      </c>
+      <c r="O285" t="n">
         <v>70.27027027027027</v>
       </c>
     </row>
@@ -18432,9 +20146,15 @@
         </is>
       </c>
       <c r="L286" t="n">
+        <v>19</v>
+      </c>
+      <c r="M286" t="n">
         <v>100</v>
       </c>
-      <c r="M286" t="n">
+      <c r="N286" t="n">
+        <v>69</v>
+      </c>
+      <c r="O286" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -18495,9 +20215,15 @@
         </is>
       </c>
       <c r="L287" t="n">
+        <v>11</v>
+      </c>
+      <c r="M287" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M287" t="n">
+      <c r="N287" t="n">
+        <v>64</v>
+      </c>
+      <c r="O287" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -18558,9 +20284,15 @@
         </is>
       </c>
       <c r="L288" t="n">
+        <v>15</v>
+      </c>
+      <c r="M288" t="n">
         <v>78.94736842105263</v>
       </c>
-      <c r="M288" t="n">
+      <c r="N288" t="n">
+        <v>60</v>
+      </c>
+      <c r="O288" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -18621,9 +20353,15 @@
         </is>
       </c>
       <c r="L289" t="n">
+        <v>4</v>
+      </c>
+      <c r="M289" t="n">
         <v>21.05263157894737</v>
       </c>
-      <c r="M289" t="n">
+      <c r="N289" t="n">
+        <v>59</v>
+      </c>
+      <c r="O289" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -18684,9 +20422,15 @@
         </is>
       </c>
       <c r="L290" t="n">
+        <v>8</v>
+      </c>
+      <c r="M290" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M290" t="n">
+      <c r="N290" t="n">
+        <v>69</v>
+      </c>
+      <c r="O290" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -18747,9 +20491,15 @@
         </is>
       </c>
       <c r="L291" t="n">
+        <v>13</v>
+      </c>
+      <c r="M291" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M291" t="n">
+      <c r="N291" t="n">
+        <v>43</v>
+      </c>
+      <c r="O291" t="n">
         <v>58.10810810810811</v>
       </c>
     </row>
@@ -18810,9 +20560,15 @@
         </is>
       </c>
       <c r="L292" t="n">
+        <v>6</v>
+      </c>
+      <c r="M292" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M292" t="n">
+      <c r="N292" t="n">
+        <v>29</v>
+      </c>
+      <c r="O292" t="n">
         <v>39.18918918918919</v>
       </c>
     </row>
@@ -18873,9 +20629,15 @@
         </is>
       </c>
       <c r="L293" t="n">
+        <v>10</v>
+      </c>
+      <c r="M293" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M293" t="n">
+      <c r="N293" t="n">
+        <v>66</v>
+      </c>
+      <c r="O293" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -18936,9 +20698,15 @@
         </is>
       </c>
       <c r="L294" t="n">
+        <v>8</v>
+      </c>
+      <c r="M294" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M294" t="n">
+      <c r="N294" t="n">
+        <v>53</v>
+      </c>
+      <c r="O294" t="n">
         <v>71.62162162162163</v>
       </c>
     </row>
@@ -18999,9 +20767,15 @@
         </is>
       </c>
       <c r="L295" t="n">
+        <v>11</v>
+      </c>
+      <c r="M295" t="n">
         <v>57.89473684210527</v>
       </c>
-      <c r="M295" t="n">
+      <c r="N295" t="n">
+        <v>67</v>
+      </c>
+      <c r="O295" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -19062,9 +20836,15 @@
         </is>
       </c>
       <c r="L296" t="n">
+        <v>5</v>
+      </c>
+      <c r="M296" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M296" t="n">
+      <c r="N296" t="n">
+        <v>55</v>
+      </c>
+      <c r="O296" t="n">
         <v>74.32432432432432</v>
       </c>
     </row>
@@ -19125,9 +20905,15 @@
         </is>
       </c>
       <c r="L297" t="n">
+        <v>9</v>
+      </c>
+      <c r="M297" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M297" t="n">
+      <c r="N297" t="n">
+        <v>61</v>
+      </c>
+      <c r="O297" t="n">
         <v>82.43243243243244</v>
       </c>
     </row>
@@ -19188,9 +20974,15 @@
         </is>
       </c>
       <c r="L298" t="n">
+        <v>8</v>
+      </c>
+      <c r="M298" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M298" t="n">
+      <c r="N298" t="n">
+        <v>64</v>
+      </c>
+      <c r="O298" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -19251,9 +21043,15 @@
         </is>
       </c>
       <c r="L299" t="n">
+        <v>10</v>
+      </c>
+      <c r="M299" t="n">
         <v>52.63157894736842</v>
       </c>
-      <c r="M299" t="n">
+      <c r="N299" t="n">
+        <v>52</v>
+      </c>
+      <c r="O299" t="n">
         <v>70.27027027027027</v>
       </c>
     </row>
@@ -19314,9 +21112,15 @@
         </is>
       </c>
       <c r="L300" t="n">
+        <v>8</v>
+      </c>
+      <c r="M300" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M300" t="n">
+      <c r="N300" t="n">
+        <v>38</v>
+      </c>
+      <c r="O300" t="n">
         <v>51.35135135135135</v>
       </c>
     </row>
@@ -19377,9 +21181,15 @@
         </is>
       </c>
       <c r="L301" t="n">
+        <v>14</v>
+      </c>
+      <c r="M301" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M301" t="n">
+      <c r="N301" t="n">
+        <v>39</v>
+      </c>
+      <c r="O301" t="n">
         <v>52.70270270270269</v>
       </c>
     </row>
@@ -19440,9 +21250,15 @@
         </is>
       </c>
       <c r="L302" t="n">
+        <v>6</v>
+      </c>
+      <c r="M302" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M302" t="n">
+      <c r="N302" t="n">
+        <v>57</v>
+      </c>
+      <c r="O302" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -19503,9 +21319,15 @@
         </is>
       </c>
       <c r="L303" t="n">
+        <v>13</v>
+      </c>
+      <c r="M303" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M303" t="n">
+      <c r="N303" t="n">
+        <v>60</v>
+      </c>
+      <c r="O303" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -19566,9 +21388,15 @@
         </is>
       </c>
       <c r="L304" t="n">
+        <v>19</v>
+      </c>
+      <c r="M304" t="n">
         <v>100</v>
       </c>
-      <c r="M304" t="n">
+      <c r="N304" t="n">
+        <v>70</v>
+      </c>
+      <c r="O304" t="n">
         <v>94.5945945945946</v>
       </c>
     </row>
@@ -19629,9 +21457,15 @@
         </is>
       </c>
       <c r="L305" t="n">
+        <v>8</v>
+      </c>
+      <c r="M305" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M305" t="n">
+      <c r="N305" t="n">
+        <v>74</v>
+      </c>
+      <c r="O305" t="n">
         <v>100</v>
       </c>
     </row>
@@ -19692,9 +21526,15 @@
         </is>
       </c>
       <c r="L306" t="n">
+        <v>14</v>
+      </c>
+      <c r="M306" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M306" t="n">
+      <c r="N306" t="n">
+        <v>57</v>
+      </c>
+      <c r="O306" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -19755,9 +21595,15 @@
         </is>
       </c>
       <c r="L307" t="n">
+        <v>8</v>
+      </c>
+      <c r="M307" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M307" t="n">
+      <c r="N307" t="n">
+        <v>57</v>
+      </c>
+      <c r="O307" t="n">
         <v>77.02702702702703</v>
       </c>
     </row>
@@ -19818,9 +21664,15 @@
         </is>
       </c>
       <c r="L308" t="n">
+        <v>3</v>
+      </c>
+      <c r="M308" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M308" t="n">
+      <c r="N308" t="n">
+        <v>50</v>
+      </c>
+      <c r="O308" t="n">
         <v>67.56756756756756</v>
       </c>
     </row>
@@ -19881,9 +21733,15 @@
         </is>
       </c>
       <c r="L309" t="n">
+        <v>9</v>
+      </c>
+      <c r="M309" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M309" t="n">
+      <c r="N309" t="n">
+        <v>28</v>
+      </c>
+      <c r="O309" t="n">
         <v>37.83783783783784</v>
       </c>
     </row>
@@ -19944,9 +21802,15 @@
         </is>
       </c>
       <c r="L310" t="n">
+        <v>3</v>
+      </c>
+      <c r="M310" t="n">
         <v>15.78947368421053</v>
       </c>
-      <c r="M310" t="n">
+      <c r="N310" t="n">
+        <v>51</v>
+      </c>
+      <c r="O310" t="n">
         <v>68.91891891891892</v>
       </c>
     </row>
@@ -20007,9 +21871,15 @@
         </is>
       </c>
       <c r="L311" t="n">
+        <v>16</v>
+      </c>
+      <c r="M311" t="n">
         <v>84.21052631578947</v>
       </c>
-      <c r="M311" t="n">
+      <c r="N311" t="n">
+        <v>63</v>
+      </c>
+      <c r="O311" t="n">
         <v>85.13513513513513</v>
       </c>
     </row>
@@ -20070,9 +21940,15 @@
         </is>
       </c>
       <c r="L312" t="n">
+        <v>7</v>
+      </c>
+      <c r="M312" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M312" t="n">
+      <c r="N312" t="n">
+        <v>59</v>
+      </c>
+      <c r="O312" t="n">
         <v>79.72972972972973</v>
       </c>
     </row>
@@ -20133,9 +22009,15 @@
         </is>
       </c>
       <c r="L313" t="n">
+        <v>13</v>
+      </c>
+      <c r="M313" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M313" t="n">
+      <c r="N313" t="n">
+        <v>67</v>
+      </c>
+      <c r="O313" t="n">
         <v>90.54054054054053</v>
       </c>
     </row>
@@ -20196,9 +22078,15 @@
         </is>
       </c>
       <c r="L314" t="n">
+        <v>8</v>
+      </c>
+      <c r="M314" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M314" t="n">
+      <c r="N314" t="n">
+        <v>25</v>
+      </c>
+      <c r="O314" t="n">
         <v>33.78378378378378</v>
       </c>
     </row>
@@ -20259,9 +22147,15 @@
         </is>
       </c>
       <c r="L315" t="n">
+        <v>8</v>
+      </c>
+      <c r="M315" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M315" t="n">
+      <c r="N315" t="n">
+        <v>27</v>
+      </c>
+      <c r="O315" t="n">
         <v>36.48648648648648</v>
       </c>
     </row>
@@ -20322,9 +22216,15 @@
         </is>
       </c>
       <c r="L316" t="n">
+        <v>6</v>
+      </c>
+      <c r="M316" t="n">
         <v>31.57894736842105</v>
       </c>
-      <c r="M316" t="n">
+      <c r="N316" t="n">
+        <v>66</v>
+      </c>
+      <c r="O316" t="n">
         <v>89.18918918918919</v>
       </c>
     </row>
@@ -20385,9 +22285,15 @@
         </is>
       </c>
       <c r="L317" t="n">
+        <v>16</v>
+      </c>
+      <c r="M317" t="n">
         <v>84.21052631578947</v>
       </c>
-      <c r="M317" t="n">
+      <c r="N317" t="n">
+        <v>60</v>
+      </c>
+      <c r="O317" t="n">
         <v>81.08108108108108</v>
       </c>
     </row>
@@ -20448,9 +22354,15 @@
         </is>
       </c>
       <c r="L318" t="n">
+        <v>9</v>
+      </c>
+      <c r="M318" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M318" t="n">
+      <c r="N318" t="n">
+        <v>69</v>
+      </c>
+      <c r="O318" t="n">
         <v>93.24324324324324</v>
       </c>
     </row>
@@ -20511,9 +22423,15 @@
         </is>
       </c>
       <c r="L319" t="n">
+        <v>2</v>
+      </c>
+      <c r="M319" t="n">
         <v>10.52631578947368</v>
       </c>
-      <c r="M319" t="n">
+      <c r="N319" t="n">
+        <v>56</v>
+      </c>
+      <c r="O319" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
@@ -20574,9 +22492,15 @@
         </is>
       </c>
       <c r="L320" t="n">
+        <v>7</v>
+      </c>
+      <c r="M320" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M320" t="n">
+      <c r="N320" t="n">
+        <v>62</v>
+      </c>
+      <c r="O320" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -20637,9 +22561,15 @@
         </is>
       </c>
       <c r="L321" t="n">
+        <v>9</v>
+      </c>
+      <c r="M321" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M321" t="n">
+      <c r="N321" t="n">
+        <v>65</v>
+      </c>
+      <c r="O321" t="n">
         <v>87.83783783783784</v>
       </c>
     </row>
@@ -20700,9 +22630,15 @@
         </is>
       </c>
       <c r="L322" t="n">
+        <v>13</v>
+      </c>
+      <c r="M322" t="n">
         <v>68.42105263157895</v>
       </c>
-      <c r="M322" t="n">
+      <c r="N322" t="n">
+        <v>64</v>
+      </c>
+      <c r="O322" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -20763,9 +22699,15 @@
         </is>
       </c>
       <c r="L323" t="n">
+        <v>9</v>
+      </c>
+      <c r="M323" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M323" t="n">
+      <c r="N323" t="n">
+        <v>18</v>
+      </c>
+      <c r="O323" t="n">
         <v>24.32432432432433</v>
       </c>
     </row>
@@ -20826,9 +22768,15 @@
         </is>
       </c>
       <c r="L324" t="n">
+        <v>7</v>
+      </c>
+      <c r="M324" t="n">
         <v>36.84210526315789</v>
       </c>
-      <c r="M324" t="n">
+      <c r="N324" t="n">
+        <v>74</v>
+      </c>
+      <c r="O324" t="n">
         <v>100</v>
       </c>
     </row>
@@ -20889,9 +22837,15 @@
         </is>
       </c>
       <c r="L325" t="n">
+        <v>5</v>
+      </c>
+      <c r="M325" t="n">
         <v>26.31578947368421</v>
       </c>
-      <c r="M325" t="n">
+      <c r="N325" t="n">
+        <v>64</v>
+      </c>
+      <c r="O325" t="n">
         <v>86.48648648648648</v>
       </c>
     </row>
@@ -20952,9 +22906,15 @@
         </is>
       </c>
       <c r="L326" t="n">
+        <v>8</v>
+      </c>
+      <c r="M326" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M326" t="n">
+      <c r="N326" t="n">
+        <v>21</v>
+      </c>
+      <c r="O326" t="n">
         <v>28.37837837837838</v>
       </c>
     </row>
@@ -21015,9 +22975,15 @@
         </is>
       </c>
       <c r="L327" t="n">
+        <v>14</v>
+      </c>
+      <c r="M327" t="n">
         <v>73.68421052631578</v>
       </c>
-      <c r="M327" t="n">
+      <c r="N327" t="n">
+        <v>62</v>
+      </c>
+      <c r="O327" t="n">
         <v>83.78378378378379</v>
       </c>
     </row>
@@ -21078,9 +23044,15 @@
         </is>
       </c>
       <c r="L328" t="n">
+        <v>8</v>
+      </c>
+      <c r="M328" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M328" t="n">
+      <c r="N328" t="n">
+        <v>34</v>
+      </c>
+      <c r="O328" t="n">
         <v>45.94594594594595</v>
       </c>
     </row>
@@ -21141,9 +23113,15 @@
         </is>
       </c>
       <c r="L329" t="n">
+        <v>8</v>
+      </c>
+      <c r="M329" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M329" t="n">
+      <c r="N329" t="n">
+        <v>47</v>
+      </c>
+      <c r="O329" t="n">
         <v>63.51351351351351</v>
       </c>
     </row>
@@ -21204,9 +23182,15 @@
         </is>
       </c>
       <c r="L330" t="n">
+        <v>8</v>
+      </c>
+      <c r="M330" t="n">
         <v>42.10526315789473</v>
       </c>
-      <c r="M330" t="n">
+      <c r="N330" t="n">
+        <v>39</v>
+      </c>
+      <c r="O330" t="n">
         <v>52.70270270270269</v>
       </c>
     </row>
@@ -21267,9 +23251,15 @@
         </is>
       </c>
       <c r="L331" t="n">
+        <v>9</v>
+      </c>
+      <c r="M331" t="n">
         <v>47.36842105263158</v>
       </c>
-      <c r="M331" t="n">
+      <c r="N331" t="n">
+        <v>56</v>
+      </c>
+      <c r="O331" t="n">
         <v>75.67567567567568</v>
       </c>
     </row>
